--- a/Översikt ÅTVIDABERG.xlsx
+++ b/Översikt ÅTVIDABERG.xlsx
@@ -601,7 +601,7 @@
         <v>46276</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         <v>28</v>
       </c>
       <c r="T2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="U2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>45853</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>45785</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46203</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45848</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45713</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>45343</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>46154</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>46276</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>45155</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>45335</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>46029</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>46181</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>46206</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>46203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44778</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>44778</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>46029</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>46276</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46029</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>45678</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>45848</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>46084</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>46086</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>45783</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>44426</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>45783</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>46084</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>46154</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>45299</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>44949</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44795</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>45896</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>44546</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>44841</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>44952</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>45156</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>44823</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>46279</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>45156</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45896</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>46084</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>44778</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>44516</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44789</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>44964</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>45259</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>44789</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>45131</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>45896</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>44631</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>45666</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45758</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>45938</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>44777</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>45111</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>44874</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>46219</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>45274</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>44789</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44851</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>44621</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>44467</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44609</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>44478</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>45323</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>45323</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>44862</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>46048</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>45379</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>46084</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>45938</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44994</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>44942</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>46112</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>46112</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>45979</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>45982</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>45565</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>45662</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>45727</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>45072</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>45072</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>46154</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>44935</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>45204</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>45468</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>46279</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
         <v>46286</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>45042</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>45323</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45222</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>44582</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>44641</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>44826</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>44539</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>44546</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>44479</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>44473</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
         <v>44467</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
         <v>44827</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>44573</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>44495</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>44467</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         <v>44782</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>44831</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>44586</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>44729</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>44467</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>44479</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>44543</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>44552</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>44531</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>44593</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>44573</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>44539</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>44838</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>44789</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>44627</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>44706</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>44789</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>44830</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>44467</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>44767</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>44683</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>44735</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>44724</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>44784</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>44732</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>44860</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>44467</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>44467</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>44514</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>44545</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>44729</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>44760</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>44778</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>44778</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>45343</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>44778</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>45362</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>45328</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>45334</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>44489</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>45378</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>45208</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>45092</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>45296</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>45222</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>45379</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>45301</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>44767</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>44833</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>45457</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>45400</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>45415</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45440</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>45308</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45308</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>44479</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>45258</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>45440</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45261</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>45796</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45267</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>45671</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45534</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>46034</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>46035</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>46035</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>46035</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>46035</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>45824</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>45740</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>44564</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44872</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45896</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>45896</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>46043</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         <v>45538</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17687,7 +17687,7 @@
         <v>46043</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17760,7 +17760,7 @@
         <v>46043</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>46043</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>46043</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>46043</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>46043</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>46045</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>46048</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>45799</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>45475</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>46045</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>46045</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>46050</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>46050</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>46049</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>46055</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>46055</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>46055</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44930</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>46034</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>45155</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>45525</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>45916</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>45916</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>45666</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>45917</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>45554</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>44876</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>46070</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>45804</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>45923</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>44516</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>45379</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>45379</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>44937</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>45932</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>46083</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>46085</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>44596</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>44631</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>44980</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>46086</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>44995</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>46091</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>44888</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>45110</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>46092</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>45597</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>46093</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21344,7 +21344,7 @@
         <v>45384</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>45939</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>44931</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>46094</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>46097</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>46099</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45946</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>44656</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>45946</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>44741</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>44895</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>44742</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>45951</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22303,7 +22303,7 @@
         <v>45951</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         <v>45415</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         <v>45415</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>45951</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>45954</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>45959</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>45308</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>44935</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45107</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>46126</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>44970</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>44988</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         <v>45225</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>45713</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>44721</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>45118</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>45608</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>45608</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>45982</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>45664</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>45982</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>45665</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         <v>44770</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>45758</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45727</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>45572</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45784</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24294,7 +24294,7 @@
         <v>45182</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>44745</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>45827</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>45993</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>45063</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>45114</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>45924</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>44546</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>44565</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>44839</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>45796</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>45229</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>45090</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>44607</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
         <v>45243</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>45736</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>45022</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>45334</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>45601</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>45077</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>44922</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>45250</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>44545</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>45835</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>45180</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>45180</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>45089</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26280,7 +26280,7 @@
         <v>45471</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44574</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26426,7 +26426,7 @@
         <v>45833</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>45833</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>45833</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>45833</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>45833</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>45229</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>46154</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>46154</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>45817</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>46155</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>46156</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>45839</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>45740</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>45837</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>45104</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27551,7 +27551,7 @@
         <v>45104</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>45727</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>45646</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27775,7 +27775,7 @@
         <v>45736</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>45387</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>45122</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27994,7 +27994,7 @@
         <v>44915</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28067,7 +28067,7 @@
         <v>46167</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>45358</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>44495</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>45665</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>45848</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>44742</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>44516</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>46171</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>45167</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>44929</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>46178</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28880,7 +28880,7 @@
         <v>46178</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>45384</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
         <v>46178</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>45040</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29172,7 +29172,7 @@
         <v>45170</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>45168</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>45122</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>46185</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>45040</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>46189</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45315</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>46189</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29761,7 +29761,7 @@
         <v>46195</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>45415</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>45334</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>46196</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>44579</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>45169</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>45187</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>45483</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>44988</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>46203</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30496,7 +30496,7 @@
         <v>46203</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30574,7 +30574,7 @@
         <v>45555</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30647,7 +30647,7 @@
         <v>46203</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>46203</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30803,7 +30803,7 @@
         <v>46204</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30881,7 +30881,7 @@
         <v>45442</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30954,7 +30954,7 @@
         <v>46252</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31027,7 +31027,7 @@
         <v>44806</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>45685</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31173,7 +31173,7 @@
         <v>44586</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>46044</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31319,7 +31319,7 @@
         <v>44621</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>45153</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
         <v>45224</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>44777</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>45113</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>45707</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31767,7 +31767,7 @@
         <v>45168</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>45715</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>45665</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>44817</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>44721</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>44721</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>44735</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>45225</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>44806</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>45695</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>45229</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>46266</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>45229</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32721,7 +32721,7 @@
         <v>46266</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>45296</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>44767</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>45217</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>46238</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>45097</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>46238</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>44938</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45323</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>44851</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>46238</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>46279</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>45296</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>46279</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>46238</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>46279</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>46279</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>46238</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>46279</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         <v>46279</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34211,7 +34211,7 @@
         <v>46280</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34284,7 +34284,7 @@
         <v>46281</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34357,7 +34357,7 @@
         <v>46239</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34430,7 +34430,7 @@
         <v>44784</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34503,7 +34503,7 @@
         <v>46281</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>46238</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>46239</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34722,7 +34722,7 @@
         <v>46239</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>46239</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>46281</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>46084</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>46029</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>46286</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>46244</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>46244</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>46286</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>46244</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>44629</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>46286</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35603,7 +35603,7 @@
         <v>46286</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>46244</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35749,7 +35749,7 @@
         <v>46286</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>46286</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>45362</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>44791</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>44517</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36119,7 +36119,7 @@
         <v>44938</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36192,7 +36192,7 @@
         <v>44897</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>44582</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36338,7 +36338,7 @@
         <v>44745</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36411,7 +36411,7 @@
         <v>44967</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36484,7 +36484,7 @@
         <v>46287</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36557,7 +36557,7 @@
         <v>45036</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         <v>45169</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>44622</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36776,7 +36776,7 @@
         <v>46289</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36849,7 +36849,7 @@
         <v>46195</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>46288</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>46288</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>45182</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37146,7 +37146,7 @@
         <v>46288</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>46288</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>46288</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37365,7 +37365,7 @@
         <v>44618</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37438,7 +37438,7 @@
         <v>46045</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37516,7 +37516,7 @@
         <v>46288</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>46289</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37662,7 +37662,7 @@
         <v>44917</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         <v>44964</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>44777</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>46288</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37959,7 +37959,7 @@
         <v>46288</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>46288</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>44972</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38183,7 +38183,7 @@
         <v>45112</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>44847</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>44812</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45440</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>44881</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38558,7 +38558,7 @@
         <v>44965</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38631,7 +38631,7 @@
         <v>45259</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45259</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38777,7 +38777,7 @@
         <v>44546</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>44949</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>44902</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>44494</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>45316</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>45077</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>45184</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45747</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>44902</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>45548</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45763</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45243</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>45348</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>45187</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>45022</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>45308</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>45072</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45720</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>44991</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40184,7 +40184,7 @@
         <v>44833</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>44831</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>44938</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>45183</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>45097</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>44973</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>45098</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>45098</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>45176</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>45205</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>44942</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45104</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>45224</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>45433</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>45217</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>45707</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41357,7 +41357,7 @@
         <v>45784</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>44223</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>44865</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41576,7 +41576,7 @@
         <v>45747</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41654,7 +41654,7 @@
         <v>45888</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41727,7 +41727,7 @@
         <v>45888</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41800,7 +41800,7 @@
         <v>46008</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41873,7 +41873,7 @@
         <v>46132</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41946,7 +41946,7 @@
         <v>46177</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>46286</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>

--- a/Översikt ÅTVIDABERG.xlsx
+++ b/Översikt ÅTVIDABERG.xlsx
@@ -601,7 +601,7 @@
         <v>46276</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>45853</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>45785</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46203</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45848</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45713</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>45343</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>46154</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>46276</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>45155</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>45335</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>46029</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>46181</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>46206</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>46203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44778</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>44778</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>46029</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>46276</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46029</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>45678</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>45848</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>46084</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>46086</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>45783</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>44426</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>45783</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>46084</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>46154</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>45299</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>44949</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44795</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>45896</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>44546</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>44841</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>44952</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>45156</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>44823</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>46279</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>45156</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45896</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>46084</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>44778</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>44516</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44789</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>44964</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>45259</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>44789</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>45131</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>45896</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>44631</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>45666</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45758</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>45938</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>44777</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>45111</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>44874</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>46219</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>45274</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>44789</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44851</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>44621</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>44467</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44609</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>44478</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>45323</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>45323</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>44862</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>46048</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>45379</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>46084</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>45938</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44994</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>44942</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>46112</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>46112</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>45979</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>45982</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>45565</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>45662</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>45727</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>45072</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>45072</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>46154</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>44935</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>45204</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>45468</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>46279</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
         <v>46286</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>45042</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>45323</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45222</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>44582</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>44641</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>44826</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>44539</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>44546</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>44479</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>44473</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
         <v>44467</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
         <v>44827</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>44573</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>44495</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>44467</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         <v>44782</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>44831</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>44586</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>44729</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>44467</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>44479</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>44543</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>44552</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>44531</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>44593</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>44573</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>44539</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>44838</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>44789</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>44627</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>44706</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>44789</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>44830</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>44467</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>44767</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>44683</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>44735</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>44724</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>44784</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>44732</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>44860</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>44467</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>44467</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>44514</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>44545</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>44729</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>44760</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>44778</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>44778</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>45343</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>44778</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>45362</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>45328</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>45334</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>44489</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>45378</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>45208</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>45092</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>45296</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>45222</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>45379</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>45301</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>44767</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>44833</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>45457</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>45400</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>45415</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45440</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>45308</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45308</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>44479</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>45258</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>45440</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45261</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>45796</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45267</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>45671</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45534</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>46034</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>46035</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>46035</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>46035</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>46035</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>45824</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>45740</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>44564</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44872</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45896</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>45896</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>46043</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         <v>45538</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17687,7 +17687,7 @@
         <v>46043</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17760,7 +17760,7 @@
         <v>46043</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>46043</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>46043</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>46043</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>46043</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>46045</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>46048</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>45799</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>45475</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>46045</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>46045</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>46050</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>46050</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>46049</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>46055</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>46055</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>46055</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44930</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>46034</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>45155</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>45525</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>45916</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>45916</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>45666</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>45917</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>45554</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>44876</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>46070</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>45804</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>45923</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>44516</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>45379</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>45379</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>44937</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>45932</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>46083</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>46085</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>44596</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>44631</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>44980</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>46086</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>44995</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>46091</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>44888</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>45110</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>46092</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>45597</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>46093</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21344,7 +21344,7 @@
         <v>45384</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>45939</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>44931</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>46094</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>46097</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>46099</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45946</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>44656</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>45946</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>44741</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>44895</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>44742</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>45951</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22303,7 +22303,7 @@
         <v>45951</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         <v>45415</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         <v>45415</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>45951</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>45954</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>45959</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>45308</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>44935</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45107</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>46126</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>44970</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>44988</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         <v>45225</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>45713</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>44721</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>45118</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>45608</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>45608</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>45982</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>45664</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>45982</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>45665</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         <v>44770</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>45758</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45727</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>45572</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45784</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24294,7 +24294,7 @@
         <v>45182</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>44745</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>45827</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>45993</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>45063</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>45114</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>45924</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>44546</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>44565</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>44839</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>45796</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>45229</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>45090</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>44607</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
         <v>45243</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>45736</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>45022</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>45334</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>45601</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>45077</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>44922</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>45250</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>44545</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>45835</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>45180</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>45180</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>45089</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26280,7 +26280,7 @@
         <v>45471</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44574</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26426,7 +26426,7 @@
         <v>45833</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>45833</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>45833</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>45833</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>45833</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>45229</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>46154</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>46154</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>45817</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>46155</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>46156</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>45839</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>45740</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>45837</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>45104</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27551,7 +27551,7 @@
         <v>45104</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>45727</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>45646</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27775,7 +27775,7 @@
         <v>45736</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>45387</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>45122</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27994,7 +27994,7 @@
         <v>44915</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28067,7 +28067,7 @@
         <v>46167</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>45358</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>44495</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>45665</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>45848</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>44742</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>44516</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>46171</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>45167</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>44929</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>46178</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28880,7 +28880,7 @@
         <v>46178</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>45384</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
         <v>46178</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>45040</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29172,7 +29172,7 @@
         <v>45170</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>45168</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>45122</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>46185</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>45040</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>46189</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45315</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>46189</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29761,7 +29761,7 @@
         <v>46195</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>45415</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>45334</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>46196</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>44579</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>45169</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>45187</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>45483</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>44988</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>46203</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30496,7 +30496,7 @@
         <v>46203</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30574,7 +30574,7 @@
         <v>45555</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30647,7 +30647,7 @@
         <v>46203</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>46203</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30803,7 +30803,7 @@
         <v>46204</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30881,7 +30881,7 @@
         <v>45442</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30954,7 +30954,7 @@
         <v>46252</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31027,7 +31027,7 @@
         <v>44806</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>45685</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31173,7 +31173,7 @@
         <v>44586</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>46044</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31319,7 +31319,7 @@
         <v>44621</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>45153</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
         <v>45224</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>44777</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>45113</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>45707</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31767,7 +31767,7 @@
         <v>45168</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>45715</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>45665</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>44817</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>44721</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>44721</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>44735</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>45225</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>44806</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>45695</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>45229</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>46266</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>45229</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32721,7 +32721,7 @@
         <v>46266</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>45296</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>44767</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>45217</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>46238</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>45097</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>46238</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>44938</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45323</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>44851</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>46238</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>46279</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>45296</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>46279</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>46238</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>46279</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>46279</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>46238</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>46279</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         <v>46279</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34211,7 +34211,7 @@
         <v>46280</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34284,7 +34284,7 @@
         <v>46281</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34357,7 +34357,7 @@
         <v>46239</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34430,7 +34430,7 @@
         <v>44784</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34503,7 +34503,7 @@
         <v>46281</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>46238</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>46239</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34722,7 +34722,7 @@
         <v>46239</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>46239</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>46281</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>46084</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>46029</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>46286</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>46244</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>46244</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>46286</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>46244</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>44629</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>46286</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35603,7 +35603,7 @@
         <v>46286</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>46244</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35749,7 +35749,7 @@
         <v>46286</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>46286</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>45362</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>44791</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>44517</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36119,7 +36119,7 @@
         <v>44938</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36192,7 +36192,7 @@
         <v>44897</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>44582</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36338,7 +36338,7 @@
         <v>44745</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36411,7 +36411,7 @@
         <v>44967</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36484,7 +36484,7 @@
         <v>46287</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36557,7 +36557,7 @@
         <v>45036</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         <v>45169</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>44622</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36776,7 +36776,7 @@
         <v>46289</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36849,7 +36849,7 @@
         <v>46195</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>46288</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>46288</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>45182</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37146,7 +37146,7 @@
         <v>46288</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>46288</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>46288</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37365,7 +37365,7 @@
         <v>44618</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37438,7 +37438,7 @@
         <v>46045</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37516,7 +37516,7 @@
         <v>46288</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>46289</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37662,7 +37662,7 @@
         <v>44917</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         <v>44964</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>44777</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>46288</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37959,7 +37959,7 @@
         <v>46288</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>46288</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>44972</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38183,7 +38183,7 @@
         <v>45112</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>44847</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>44812</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45440</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>44881</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38558,7 +38558,7 @@
         <v>44965</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38631,7 +38631,7 @@
         <v>45259</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45259</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38777,7 +38777,7 @@
         <v>44546</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>44949</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>44902</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>44494</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>45316</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>45077</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>45184</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45747</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>44902</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>45548</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45763</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45243</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>45348</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>45187</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>45022</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>45308</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>45072</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45720</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>44991</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40184,7 +40184,7 @@
         <v>44833</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>44831</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>44938</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>45183</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>45097</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>44973</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>45098</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>45098</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>45176</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>45205</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>44942</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45104</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>45224</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>45433</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>45217</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>45707</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41357,7 +41357,7 @@
         <v>45784</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>44223</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>44865</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41576,7 +41576,7 @@
         <v>45747</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41654,7 +41654,7 @@
         <v>45888</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41727,7 +41727,7 @@
         <v>45888</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41800,7 +41800,7 @@
         <v>46008</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41873,7 +41873,7 @@
         <v>46132</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41946,7 +41946,7 @@
         <v>46177</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>46286</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>

--- a/Översikt ÅTVIDABERG.xlsx
+++ b/Översikt ÅTVIDABERG.xlsx
@@ -601,7 +601,7 @@
         <v>46276</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         <v>28</v>
       </c>
       <c r="T2" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="U2" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>45853</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>45785</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46203</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45848</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45713</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>45343</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>45335</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>46154</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46276</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>46029</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>46181</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>46206</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>44778</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>46203</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>46029</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>46276</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>46029</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>44778</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>45678</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>45848</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>46084</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>46086</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>45783</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>44426</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>45783</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>44949</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>46084</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>46154</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>45299</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44795</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>45896</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>44546</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>44841</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>45156</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>44823</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>45156</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>46279</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>44952</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45896</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>46084</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>44778</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>44516</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45259</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>44964</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>44789</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>44789</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>44874</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>44631</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>45896</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>45938</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>45274</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>45131</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>44777</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>46219</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         <v>45666</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>45111</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>45758</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>44789</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44851</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>44621</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>44609</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44478</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>45072</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44942</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>44935</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>45072</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>46048</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>45938</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>46084</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>45662</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>45979</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>46112</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>46112</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>45323</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>44994</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45982</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>45565</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>45323</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>46154</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>45204</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>45222</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>44862</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>46279</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>45042</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>46286</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>45379</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>45727</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>45468</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>45323</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>44641</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>44582</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>44539</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44826</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>44546</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>44479</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44473</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>44827</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>44573</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>44495</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>44782</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>44831</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>44586</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>44729</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>44479</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>44543</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>44552</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>44531</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>44593</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>44573</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>44539</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>44838</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>44789</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>44627</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>44706</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>44789</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>44830</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>44767</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>44735</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44683</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>44724</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>44784</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>44732</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>44860</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44514</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44545</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>44729</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>44760</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>44778</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>44778</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44629</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45362</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>44888</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>44967</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>44579</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>44847</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>44991</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>44973</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>44831</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>44895</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45548</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>44949</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>44494</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45114</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44621</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45440</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45077</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>44745</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>45222</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>44742</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>45036</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>44516</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>45348</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44777</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>45167</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45113</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>44806</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45665</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45301</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45415</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>44778</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>45089</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>45824</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>45534</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>45740</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>45896</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>45664</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45896</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>46034</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>46035</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>44479</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>46043</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>46043</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>46043</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>46043</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>46043</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>46043</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>45796</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>45308</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>46045</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>46045</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>44770</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>45671</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>46045</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         <v>46049</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>46048</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>45917</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>45916</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>45916</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45799</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>46050</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>45804</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>46050</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>46055</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>44607</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>46055</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>46055</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>45362</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19088,7 +19088,7 @@
         <v>45923</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>45180</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>46034</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>44897</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>45475</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>45323</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>45932</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>44622</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>46070</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>45939</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>45187</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>45229</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>45224</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>45110</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45946</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>45946</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>45951</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>45951</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>45229</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>46083</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>45229</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>45433</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>46086</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>46085</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>45954</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>45122</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>46091</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>46092</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>46094</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>45259</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>45259</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>46097</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>46099</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>44767</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>45713</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>45982</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45982</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>44721</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45334</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>44767</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45358</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>45217</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45072</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>45608</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>45608</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>44937</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45833</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45833</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45833</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>45205</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>44876</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45077</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>44935</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>45343</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45572</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45827</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45796</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45837</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45784</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45707</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>44988</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45695</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>45727</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>45924</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>45736</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>45169</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>45646</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>44872</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>45758</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45685</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>44812</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24361,7 +24361,7 @@
         <v>45104</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>45104</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>44833</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>45665</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>45168</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>45665</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45727</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>45022</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>45848</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>44938</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>45835</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>44791</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>44938</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>44929</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>45736</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>45229</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>44988</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>45296</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>45601</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>45384</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45170</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>44586</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>45176</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>44574</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>45740</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>45415</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>45118</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>45187</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45415</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>44851</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>44777</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45817</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45217</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>46154</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>46155</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>46154</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>46156</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>44565</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>44545</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>45839</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>44517</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45308</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>44938</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>46167</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45040</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>44980</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>45107</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>44942</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>45440</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>46171</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>45092</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>44516</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>45379</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>45747</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>45315</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>46178</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>46178</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>44546</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>45250</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>46178</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>45308</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>45554</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>45267</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>44721</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>44995</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29136,7 +29136,7 @@
         <v>44721</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>45208</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>44964</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>45457</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29438,7 +29438,7 @@
         <v>46185</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>46189</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29584,7 +29584,7 @@
         <v>45440</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29657,7 +29657,7 @@
         <v>44833</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>46189</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29803,7 +29803,7 @@
         <v>46196</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>46195</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29949,7 +29949,7 @@
         <v>44735</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>44741</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>46203</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30173,7 +30173,7 @@
         <v>46204</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>46203</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>46203</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44881</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30480,7 +30480,7 @@
         <v>44931</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>46044</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>44489</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30704,7 +30704,7 @@
         <v>44806</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30777,7 +30777,7 @@
         <v>45097</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30850,7 +30850,7 @@
         <v>45155</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30923,7 +30923,7 @@
         <v>45104</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>46266</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>45442</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>46266</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31220,7 +31220,7 @@
         <v>46238</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>46238</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31366,7 +31366,7 @@
         <v>45378</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31439,7 +31439,7 @@
         <v>45483</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31512,7 +31512,7 @@
         <v>44972</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>46279</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>46279</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>45666</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>46279</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>46279</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>46279</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>46279</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>46281</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>45555</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>46280</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>46239</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32418,7 +32418,7 @@
         <v>46281</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32491,7 +32491,7 @@
         <v>46281</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>46239</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>46239</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>46238</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32783,7 +32783,7 @@
         <v>46239</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>44970</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>45538</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33002,7 +33002,7 @@
         <v>44930</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>45090</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44495</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>45098</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>45098</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33372,7 +33372,7 @@
         <v>45063</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33450,7 +33450,7 @@
         <v>45243</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33523,7 +33523,7 @@
         <v>45334</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33596,7 +33596,7 @@
         <v>45243</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>46286</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>46286</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>46084</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>46286</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>46286</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>45022</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>44902</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>46244</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34258,7 +34258,7 @@
         <v>45225</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34331,7 +34331,7 @@
         <v>46286</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>44922</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>46244</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34550,7 +34550,7 @@
         <v>46029</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>46244</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34696,7 +34696,7 @@
         <v>46287</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>46244</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>46288</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34915,7 +34915,7 @@
         <v>46288</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>46288</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35066,7 +35066,7 @@
         <v>46288</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35139,7 +35139,7 @@
         <v>46288</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>46289</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>44631</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35358,7 +35358,7 @@
         <v>44917</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35431,7 +35431,7 @@
         <v>46288</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35504,7 +35504,7 @@
         <v>46288</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>46288</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35655,7 +35655,7 @@
         <v>46288</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35733,7 +35733,7 @@
         <v>45169</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35806,7 +35806,7 @@
         <v>45097</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35879,7 +35879,7 @@
         <v>45224</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35952,7 +35952,7 @@
         <v>44618</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36025,7 +36025,7 @@
         <v>44742</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>46035</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>45387</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36244,7 +36244,7 @@
         <v>46289</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36317,7 +36317,7 @@
         <v>46290</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36390,7 +36390,7 @@
         <v>45122</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>44745</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36536,7 +36536,7 @@
         <v>45183</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>46045</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45400</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>46195</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>46295</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>44965</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>45471</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>44817</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>46294</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37198,7 +37198,7 @@
         <v>46294</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>45328</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37344,7 +37344,7 @@
         <v>46252</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>45597</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>45225</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37563,7 +37563,7 @@
         <v>46093</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>46203</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>46295</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37792,7 +37792,7 @@
         <v>45379</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37865,7 +37865,7 @@
         <v>45379</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>45112</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38016,7 +38016,7 @@
         <v>46238</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>45184</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38162,7 +38162,7 @@
         <v>46238</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38235,7 +38235,7 @@
         <v>46297</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>45316</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>45833</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>46238</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>46295</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38615,7 +38615,7 @@
         <v>46286</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38688,7 +38688,7 @@
         <v>44564</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45182</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>45334</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>44839</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>44784</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45258</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39131,7 +39131,7 @@
         <v>45384</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39204,7 +39204,7 @@
         <v>45763</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39277,7 +39277,7 @@
         <v>45040</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>44596</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39423,7 +39423,7 @@
         <v>45296</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>45720</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>45308</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>44902</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>45525</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>45715</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>45168</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39939,7 +39939,7 @@
         <v>45153</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>45180</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>45182</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40158,7 +40158,7 @@
         <v>44582</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40231,7 +40231,7 @@
         <v>45415</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40304,7 +40304,7 @@
         <v>44546</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40382,7 +40382,7 @@
         <v>44915</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45296</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>45261</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>44656</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>45707</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>45784</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>44223</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>44865</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         <v>45747</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41044,7 +41044,7 @@
         <v>45888</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         <v>45888</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>46008</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>46132</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>46177</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41409,7 +41409,7 @@
         <v>46286</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>

--- a/Översikt ÅTVIDABERG.xlsx
+++ b/Översikt ÅTVIDABERG.xlsx
@@ -601,7 +601,7 @@
         <v>46276</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         <v>28</v>
       </c>
       <c r="T2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="U2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>45853</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>45785</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46203</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45848</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45713</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>45343</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>45335</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>46154</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46276</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>46029</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>46181</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>46206</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>44778</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>46203</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>46029</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>46276</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>46029</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>44778</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>45678</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>45848</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>46084</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>46086</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>45783</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>44426</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>45783</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>44949</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>46084</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>46154</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>45299</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44795</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>45896</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>44546</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>44841</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>45156</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>44823</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>45156</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>46279</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>44952</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45896</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>46084</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>44778</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>44516</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45259</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>44964</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>44789</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>44789</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>44874</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>44631</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>45896</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>45938</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>45274</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>45131</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>44777</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>46219</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         <v>45666</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>45111</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>45758</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>44789</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44851</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>44621</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>44609</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44478</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>45072</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44942</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>44935</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>45072</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>46048</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>45938</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>46084</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>45662</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>45979</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>46112</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>46112</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>45323</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>44994</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45982</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>45565</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>45323</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>46154</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>45204</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>45222</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>44862</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>46279</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>45042</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>46286</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>45379</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>45727</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>45468</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>45323</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>44641</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>44582</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>44539</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44826</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>44546</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>44479</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44473</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>44827</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>44573</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>44495</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>44782</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>44831</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>44586</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>44729</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>44479</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>44543</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>44552</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>44531</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>44593</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>44573</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>44539</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>44838</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>44789</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>44627</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>44706</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>44789</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>44830</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>44767</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>44735</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44683</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>44724</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>44784</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>44732</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>44860</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44514</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44545</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>44729</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>44760</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>44778</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>44778</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44629</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45362</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>44888</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>44967</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>44579</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>44847</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>44991</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>44973</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>44831</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>44895</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45548</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>44949</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>44494</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45114</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44621</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45440</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45077</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>44745</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>45222</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>44742</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>45036</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>44516</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>45348</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44777</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>45167</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45113</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>44806</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45665</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45301</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45415</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>44778</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>45089</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>45824</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>45534</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>45740</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>45896</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>45664</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45896</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>46034</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>46035</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>44479</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>46043</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>46043</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>46043</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>46043</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>46043</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>46043</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>45796</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>45308</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>46045</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>46045</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>44770</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>45671</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>46045</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         <v>46049</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>46048</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>45917</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>45916</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>45916</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45799</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>46050</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>45804</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>46050</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>46055</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>44607</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>46055</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>46055</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>45362</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19088,7 +19088,7 @@
         <v>45923</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>45180</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>46034</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>44897</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>45475</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>45323</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>45932</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>44622</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>46070</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>45939</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>45187</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>45229</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>45224</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>45110</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45946</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>45946</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>45951</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>45951</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>45229</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>46083</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>45229</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>45433</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>46086</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>46085</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>45954</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>45122</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>46091</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>46092</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>46094</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>45259</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>45259</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>46097</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>46099</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>44767</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>45713</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>45982</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45982</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>44721</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45334</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>44767</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45358</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>45217</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45072</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>45608</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>45608</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>44937</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45833</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45833</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45833</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>45205</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>44876</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45077</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>44935</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>45343</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45572</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45827</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45796</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45837</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45784</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45707</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>44988</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45695</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>45727</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>45924</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>45736</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>45169</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>45646</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>44872</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>45758</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45685</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>44812</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24361,7 +24361,7 @@
         <v>45104</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>45104</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>44833</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>45665</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>45168</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>45665</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45727</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>45022</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>45848</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>44938</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>45835</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>44791</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>44938</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>44929</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>45736</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>45229</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>44988</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>45296</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>45601</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>45384</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45170</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>44586</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>45176</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>44574</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>45740</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>45415</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>45118</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>45187</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45415</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>44851</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>44777</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45817</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45217</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>46154</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>46155</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>46154</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>46156</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>44565</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>44545</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>45839</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>44517</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45308</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>44938</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>46167</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45040</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>44980</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>45107</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>44942</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>45440</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>46171</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>45092</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>44516</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>45379</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>45747</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>45315</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>46178</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>46178</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>44546</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>45250</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>46178</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>45308</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>45554</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>45267</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>44721</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>44995</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29136,7 +29136,7 @@
         <v>44721</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>45208</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>44964</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>45457</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29438,7 +29438,7 @@
         <v>46185</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>46189</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29584,7 +29584,7 @@
         <v>45440</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29657,7 +29657,7 @@
         <v>44833</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>46189</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29803,7 +29803,7 @@
         <v>46196</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>46195</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29949,7 +29949,7 @@
         <v>44735</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>44741</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>46203</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30173,7 +30173,7 @@
         <v>46204</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>46203</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>46203</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>44881</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30480,7 +30480,7 @@
         <v>44931</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>46044</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>44489</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30704,7 +30704,7 @@
         <v>44806</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30777,7 +30777,7 @@
         <v>45097</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30850,7 +30850,7 @@
         <v>45155</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30923,7 +30923,7 @@
         <v>45104</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>46266</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>45442</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>46266</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31220,7 +31220,7 @@
         <v>46238</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>46238</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31366,7 +31366,7 @@
         <v>45378</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31439,7 +31439,7 @@
         <v>45483</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31512,7 +31512,7 @@
         <v>44972</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>46279</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>46279</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>45666</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>46279</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>46279</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>46279</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>46279</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>46281</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>45555</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>46280</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>46239</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32418,7 +32418,7 @@
         <v>46281</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32491,7 +32491,7 @@
         <v>46281</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>46239</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>46239</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>46238</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32783,7 +32783,7 @@
         <v>46239</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>44970</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>45538</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33002,7 +33002,7 @@
         <v>44930</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>45090</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44495</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>45098</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>45098</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33372,7 +33372,7 @@
         <v>45063</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33450,7 +33450,7 @@
         <v>45243</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33523,7 +33523,7 @@
         <v>45334</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33596,7 +33596,7 @@
         <v>45243</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>46286</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>46286</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>46084</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>46286</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>46286</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>45022</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>44902</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>46244</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34258,7 +34258,7 @@
         <v>45225</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34331,7 +34331,7 @@
         <v>46286</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>44922</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>46244</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34550,7 +34550,7 @@
         <v>46029</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>46244</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34696,7 +34696,7 @@
         <v>46287</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>46244</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>46288</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34915,7 +34915,7 @@
         <v>46288</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>46288</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35066,7 +35066,7 @@
         <v>46288</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35139,7 +35139,7 @@
         <v>46288</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>46289</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>44631</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35358,7 +35358,7 @@
         <v>44917</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35431,7 +35431,7 @@
         <v>46288</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35504,7 +35504,7 @@
         <v>46288</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>46288</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35655,7 +35655,7 @@
         <v>46288</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35733,7 +35733,7 @@
         <v>45169</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35806,7 +35806,7 @@
         <v>45097</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35879,7 +35879,7 @@
         <v>45224</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35952,7 +35952,7 @@
         <v>44618</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36025,7 +36025,7 @@
         <v>44742</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>46035</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>45387</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36244,7 +36244,7 @@
         <v>46289</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36317,7 +36317,7 @@
         <v>46290</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36390,7 +36390,7 @@
         <v>45122</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>44745</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36536,7 +36536,7 @@
         <v>45183</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>46045</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45400</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>46195</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>46295</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>44965</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>45471</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>44817</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>46294</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37198,7 +37198,7 @@
         <v>46294</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>45328</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37344,7 +37344,7 @@
         <v>46252</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>45597</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>45225</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37563,7 +37563,7 @@
         <v>46093</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37636,7 +37636,7 @@
         <v>46203</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>46295</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37792,7 +37792,7 @@
         <v>45379</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37865,7 +37865,7 @@
         <v>45379</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>45112</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38016,7 +38016,7 @@
         <v>46238</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>45184</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38162,7 +38162,7 @@
         <v>46238</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38235,7 +38235,7 @@
         <v>46297</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>45316</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>45833</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>46238</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>46295</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38615,7 +38615,7 @@
         <v>46286</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38688,7 +38688,7 @@
         <v>44564</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45182</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>45334</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>44839</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>44784</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45258</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39131,7 +39131,7 @@
         <v>45384</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39204,7 +39204,7 @@
         <v>45763</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39277,7 +39277,7 @@
         <v>45040</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>44596</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39423,7 +39423,7 @@
         <v>45296</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>45720</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>45308</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>44902</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>45525</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>45715</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>45168</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39939,7 +39939,7 @@
         <v>45153</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>45180</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>45182</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40158,7 +40158,7 @@
         <v>44582</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40231,7 +40231,7 @@
         <v>45415</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40304,7 +40304,7 @@
         <v>44546</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40382,7 +40382,7 @@
         <v>44915</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45296</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>45261</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>44656</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>45707</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>45784</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>44223</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>44865</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         <v>45747</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41044,7 +41044,7 @@
         <v>45888</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         <v>45888</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>46008</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>46132</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>46177</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41409,7 +41409,7 @@
         <v>46286</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>

--- a/Översikt ÅTVIDABERG.xlsx
+++ b/Översikt ÅTVIDABERG.xlsx
@@ -601,7 +601,7 @@
         <v>46276</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>45853</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>45785</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46203</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45848</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45713</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>45343</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>45335</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>46154</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46276</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>46029</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>46181</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>46206</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>44778</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>46203</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>44778</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>46276</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>46029</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46029</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>45678</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>45783</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>45848</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>46084</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>46086</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>44426</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>45783</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>45299</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44949</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>46084</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>46154</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44795</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>45896</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>44546</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>45156</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>44841</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45156</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>44952</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>44823</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>46279</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45896</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>44778</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>46084</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>44516</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44789</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>44964</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>45259</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>44789</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>45131</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>45896</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>44631</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>45666</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45758</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>45938</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>44874</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>44777</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>45274</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>45111</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>46112</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>46219</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>44789</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>44851</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>44621</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>44609</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>44862</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>45323</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>45323</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>45042</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>45323</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>45222</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>44935</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>45379</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>45938</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>44994</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>44942</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>45662</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>45204</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>45468</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45727</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>45979</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45072</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>45072</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>46112</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45982</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45565</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>46048</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>46154</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>46084</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>46279</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>46286</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>46301</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>44582</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>44641</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44826</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>44539</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>44546</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44479</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>44827</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>44573</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>44495</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>44782</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>44831</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>44586</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>44729</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         <v>44479</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>44543</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>44627</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>44552</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>44706</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12404,7 +12404,7 @@
         <v>44531</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>44735</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         <v>44593</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>44683</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>44573</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>44724</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>44789</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>44830</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>44784</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13066,7 +13066,7 @@
         <v>44539</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
         <v>44514</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>44838</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>44732</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13363,7 +13363,7 @@
         <v>44789</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>44767</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>44545</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>44860</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>45378</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>44729</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>44760</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13884,7 +13884,7 @@
         <v>44778</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>44778</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>45077</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>45184</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14176,7 +14176,7 @@
         <v>45089</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>45471</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>45747</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>45229</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>45092</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>44902</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>45548</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>45222</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>45343</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>45763</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>44778</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>45362</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>45328</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>45334</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>45243</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>45740</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>45104</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45104</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         <v>45296</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>45379</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>45301</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>44833</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>45400</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45415</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>44767</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>44489</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>45208</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>45348</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>45387</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>45457</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>45122</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45440</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>45187</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44915</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>45358</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>45308</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>45022</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
         <v>45308</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>44479</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>45072</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>45258</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>45720</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>44991</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>44833</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>45440</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>45261</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>44495</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>44831</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>44938</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>44742</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17871,7 +17871,7 @@
         <v>45183</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         <v>45267</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>45097</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>44973</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>45167</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>45098</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45098</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>45176</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>45534</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>45205</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>44942</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         <v>45104</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>45824</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>45740</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         <v>45896</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>45896</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19054,7 +19054,7 @@
         <v>45224</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>45433</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>44564</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>44872</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>45217</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>45538</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>45707</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>45475</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>45384</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45040</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>45784</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>45916</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>44930</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>45168</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>45917</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>45155</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>45525</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>45122</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>45040</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>45666</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>45554</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44876</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>45923</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>45315</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>45415</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>45334</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45308</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>44516</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>44579</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>45379</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>45379</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>44937</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>45796</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45169</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>45932</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21624,7 +21624,7 @@
         <v>45187</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>45483</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>45671</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>44596</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>44631</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>44980</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>44995</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22140,7 +22140,7 @@
         <v>44988</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22213,7 +22213,7 @@
         <v>45555</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>44888</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>45799</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>45597</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>45384</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>44931</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>45804</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45442</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>44656</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44741</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44806</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>44895</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>44742</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>45110</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>45939</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45415</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>45415</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>45946</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>45946</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23620,7 +23620,7 @@
         <v>45713</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>45685</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>44935</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>45107</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>44586</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>45951</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>44970</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         <v>44621</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>44988</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>45225</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>45153</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>45954</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>45833</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45224</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>45833</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>44777</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>45113</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>45707</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>44721</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>45168</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>45715</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>45118</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>45665</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>45837</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>45608</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>45608</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>44817</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25636,7 +25636,7 @@
         <v>45664</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>44721</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44721</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>44735</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>45225</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>44806</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>44770</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>45695</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>45727</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>45646</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26371,7 +26371,7 @@
         <v>45229</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>45736</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26517,7 +26517,7 @@
         <v>45182</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26590,7 +26590,7 @@
         <v>44745</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26663,7 +26663,7 @@
         <v>45229</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26736,7 +26736,7 @@
         <v>45063</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>45114</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>45665</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>45848</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27033,7 +27033,7 @@
         <v>45296</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44546</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>44767</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>45217</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>44929</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>45097</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>44565</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
         <v>44839</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>44938</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>45323</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>45170</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>45229</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>44851</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>45982</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45090</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>44607</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>45243</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>46097</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>45022</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>45982</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>46099</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>45334</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>45296</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>45077</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>44922</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>45250</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>44545</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>44784</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29087,7 +29087,7 @@
         <v>45180</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29160,7 +29160,7 @@
         <v>45180</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>44629</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
         <v>45362</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44791</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>44517</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>44938</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>44897</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>44582</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29749,7 +29749,7 @@
         <v>44745</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>44967</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29895,7 +29895,7 @@
         <v>45036</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>44622</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>45665</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>45758</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>45727</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>45182</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>45572</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30406,7 +30406,7 @@
         <v>44618</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>45784</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>45827</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>44917</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>44964</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>44777</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>44972</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30917,7 +30917,7 @@
         <v>45924</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>45112</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31068,7 +31068,7 @@
         <v>44847</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>44812</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>46034</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>46035</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31365,7 +31365,7 @@
         <v>45796</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>45440</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>44881</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>44965</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>46043</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>45259</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>45259</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31881,7 +31881,7 @@
         <v>44546</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>46043</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32032,7 +32032,7 @@
         <v>46043</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>46043</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>45736</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>46043</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>46043</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32407,7 +32407,7 @@
         <v>46045</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         <v>46048</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>45601</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>46045</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>44949</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>46045</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>44902</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44494</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>46050</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>46050</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45316</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>46049</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>45835</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>46055</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>46055</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>46055</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33610,7 +33610,7 @@
         <v>46034</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33683,7 +33683,7 @@
         <v>46070</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>44574</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33834,7 +33834,7 @@
         <v>46154</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33907,7 +33907,7 @@
         <v>46154</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>46083</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45817</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>46085</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>46086</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>46156</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>45839</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>46092</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>46167</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>44516</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>46171</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>46178</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34798,7 +34798,7 @@
         <v>46178</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>46178</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>46185</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>46189</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>46195</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>46203</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>46203</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>46204</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35397,7 +35397,7 @@
         <v>46044</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>46266</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>46266</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>46238</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35689,7 +35689,7 @@
         <v>46238</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>46279</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>46279</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>46279</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>46279</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36074,7 +36074,7 @@
         <v>46279</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>46279</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>46280</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>46281</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>46239</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>46281</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>46238</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>46239</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>46239</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>46239</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>46281</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>46084</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36965,7 +36965,7 @@
         <v>46029</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>46286</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>46244</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>46244</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>46286</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>46244</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37403,7 +37403,7 @@
         <v>46286</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>46286</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37549,7 +37549,7 @@
         <v>46244</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>46286</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37695,7 +37695,7 @@
         <v>46287</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37768,7 +37768,7 @@
         <v>45169</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37841,7 +37841,7 @@
         <v>46289</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37914,7 +37914,7 @@
         <v>46195</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37987,7 +37987,7 @@
         <v>46288</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>46288</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>46288</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38211,7 +38211,7 @@
         <v>46288</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38284,7 +38284,7 @@
         <v>46288</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38357,7 +38357,7 @@
         <v>46045</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>46288</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>46289</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>46288</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>46288</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>46288</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>46252</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>46035</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38956,7 +38956,7 @@
         <v>46290</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39029,7 +39029,7 @@
         <v>46294</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39102,7 +39102,7 @@
         <v>46294</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>46238</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>46238</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39321,7 +39321,7 @@
         <v>46295</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>46238</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>46295</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>46295</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39623,7 +39623,7 @@
         <v>46093</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
         <v>46297</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>46203</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>46286</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>46301</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40003,7 +40003,7 @@
         <v>46301</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40081,7 +40081,7 @@
         <v>46301</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>46301</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>46301</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>46301</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>45833</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40461,7 +40461,7 @@
         <v>46303</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40539,7 +40539,7 @@
         <v>45916</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>45308</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>46303</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40763,7 +40763,7 @@
         <v>46189</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>46091</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40909,7 +40909,7 @@
         <v>45833</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>45951</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41060,7 +41060,7 @@
         <v>44223</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41133,7 +41133,7 @@
         <v>44865</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41206,7 +41206,7 @@
         <v>45747</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>45888</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41357,7 +41357,7 @@
         <v>45888</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>46008</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>46132</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41576,7 +41576,7 @@
         <v>46177</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>46286</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>

--- a/Översikt ÅTVIDABERG.xlsx
+++ b/Översikt ÅTVIDABERG.xlsx
@@ -601,7 +601,7 @@
         <v>46276</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>45853</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>45785</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46203</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45848</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45713</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>45343</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>45335</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>46154</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46276</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>46029</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>46181</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>46206</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>44778</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>46203</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>44778</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>46276</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>46029</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46029</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>45678</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>45783</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>45848</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>46084</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>46086</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>44426</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>45783</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>45299</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44949</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>46084</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>46154</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44795</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>45896</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>44546</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>45156</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>44841</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45156</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>44952</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>44823</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>46279</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45896</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>44778</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>46084</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>44516</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44789</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>44964</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>45259</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>44789</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>45131</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>45896</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>44631</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>45666</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45758</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>45938</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>44874</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>44777</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>45274</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>45111</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>46112</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>46219</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>44789</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>44851</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>44621</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>44609</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>44862</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>45323</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>45323</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>45042</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>45323</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>45222</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>44935</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>45379</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>45938</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>44994</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>44942</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>45662</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>45204</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>45468</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45727</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>45979</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45072</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>45072</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>46112</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45982</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>45565</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>46048</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>46154</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>46084</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>46279</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>46286</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>46301</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>44582</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>44641</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44826</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>44539</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>44546</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44479</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>44827</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>44573</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>44495</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>44782</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>44831</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>44586</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>44729</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         <v>44479</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>44543</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>44627</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>44552</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>44706</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12404,7 +12404,7 @@
         <v>44531</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>44735</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         <v>44593</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>44683</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>44573</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>44724</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>44789</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>44830</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>44784</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13066,7 +13066,7 @@
         <v>44539</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
         <v>44514</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>44838</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>44732</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13363,7 +13363,7 @@
         <v>44789</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>44767</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>44545</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>44860</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>45378</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>44729</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>44760</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13884,7 +13884,7 @@
         <v>44778</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>44778</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>45077</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>45184</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14176,7 +14176,7 @@
         <v>45089</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>45471</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>45747</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>45229</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>45092</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>44902</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>45548</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>45222</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>45343</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>45763</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>44778</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>45362</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>45328</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>45334</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>45243</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>45740</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>45104</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45104</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         <v>45296</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>45379</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>45301</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>44833</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>45400</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45415</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>44767</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>44489</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>45208</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>45348</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>45387</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>45457</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>45122</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45440</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>45187</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44915</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>45358</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>45308</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>45022</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
         <v>45308</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>44479</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>45072</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>45258</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>45720</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>44991</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>44833</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>45440</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>45261</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>44495</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>44831</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>44938</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>44742</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17871,7 +17871,7 @@
         <v>45183</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         <v>45267</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>45097</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>44973</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>45167</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>45098</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45098</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>45176</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>45534</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>45205</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>44942</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         <v>45104</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>45824</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>45740</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         <v>45896</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>45896</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19054,7 +19054,7 @@
         <v>45224</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>45433</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>44564</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>44872</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>45217</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>45538</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>45707</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>45475</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>45384</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45040</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>45784</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>45916</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>44930</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>45168</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>45917</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>45155</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>45525</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>45122</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>45040</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>45666</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>45554</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44876</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>45923</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>45315</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>45415</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>45334</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45308</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>44516</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>44579</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>45379</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>45379</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>44937</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>45796</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45169</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>45932</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21624,7 +21624,7 @@
         <v>45187</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>45483</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>45671</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>44596</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>44631</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>44980</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>44995</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22140,7 +22140,7 @@
         <v>44988</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22213,7 +22213,7 @@
         <v>45555</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>44888</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>45799</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>45597</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>45384</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>44931</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>45804</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45442</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>44656</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44741</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44806</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>44895</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>44742</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>45110</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>45939</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45415</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>45415</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>45946</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>45946</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23620,7 +23620,7 @@
         <v>45713</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>45685</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>44935</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>45107</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>44586</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>45951</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>44970</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         <v>44621</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>44988</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>45225</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>45153</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>45954</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>45833</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45224</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>45833</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>44777</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>45113</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>45707</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>44721</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>45168</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>45715</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>45118</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>45665</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>45837</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>45608</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>45608</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>44817</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25636,7 +25636,7 @@
         <v>45664</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>44721</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>44721</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>44735</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>45225</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>44806</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>44770</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>45695</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>45727</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>45646</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26371,7 +26371,7 @@
         <v>45229</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>45736</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26517,7 +26517,7 @@
         <v>45182</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26590,7 +26590,7 @@
         <v>44745</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26663,7 +26663,7 @@
         <v>45229</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26736,7 +26736,7 @@
         <v>45063</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>45114</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>45665</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>45848</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27033,7 +27033,7 @@
         <v>45296</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44546</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>44767</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>45217</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>44929</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>45097</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>44565</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
         <v>44839</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>44938</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>45323</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>45170</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>45229</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>44851</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>45982</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45090</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>44607</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>45243</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>46097</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>45022</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>45982</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>46099</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>45334</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>45296</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>45077</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>44922</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>45250</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>44545</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>44784</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29087,7 +29087,7 @@
         <v>45180</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29160,7 +29160,7 @@
         <v>45180</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>44629</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
         <v>45362</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>44791</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>44517</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>44938</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>44897</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>44582</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29749,7 +29749,7 @@
         <v>44745</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>44967</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29895,7 +29895,7 @@
         <v>45036</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>44622</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>45665</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>45758</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>45727</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>45182</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>45572</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30406,7 +30406,7 @@
         <v>44618</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>45784</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>45827</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>44917</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>44964</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>44777</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>44972</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30917,7 +30917,7 @@
         <v>45924</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>45112</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31068,7 +31068,7 @@
         <v>44847</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>44812</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>46034</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>46035</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31365,7 +31365,7 @@
         <v>45796</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>45440</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>44881</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>44965</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>46043</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>45259</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>45259</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31881,7 +31881,7 @@
         <v>44546</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>46043</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32032,7 +32032,7 @@
         <v>46043</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>46043</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>45736</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>46043</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>46043</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32407,7 +32407,7 @@
         <v>46045</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         <v>46048</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>45601</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>46045</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>44949</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>46045</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>44902</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44494</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>46050</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>46050</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45316</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>46049</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>45835</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>46055</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>46055</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>46055</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33610,7 +33610,7 @@
         <v>46034</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33683,7 +33683,7 @@
         <v>46070</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>44574</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33834,7 +33834,7 @@
         <v>46154</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33907,7 +33907,7 @@
         <v>46154</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>46083</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45817</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>46085</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>46086</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>46156</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>45839</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>46092</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>46167</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>44516</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>46171</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>46178</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34798,7 +34798,7 @@
         <v>46178</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>46178</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>46185</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>46189</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>46195</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>46203</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>46203</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>46204</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35397,7 +35397,7 @@
         <v>46044</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>46266</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>46266</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>46238</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35689,7 +35689,7 @@
         <v>46238</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>46279</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>46279</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>46279</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>46279</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36074,7 +36074,7 @@
         <v>46279</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>46279</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>46280</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>46281</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>46239</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>46281</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>46238</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>46239</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>46239</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>46239</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>46281</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>46084</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36965,7 +36965,7 @@
         <v>46029</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>46286</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>46244</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>46244</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>46286</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>46244</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37403,7 +37403,7 @@
         <v>46286</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>46286</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37549,7 +37549,7 @@
         <v>46244</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>46286</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37695,7 +37695,7 @@
         <v>46287</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37768,7 +37768,7 @@
         <v>45169</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37841,7 +37841,7 @@
         <v>46289</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37914,7 +37914,7 @@
         <v>46195</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37987,7 +37987,7 @@
         <v>46288</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>46288</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>46288</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38211,7 +38211,7 @@
         <v>46288</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38284,7 +38284,7 @@
         <v>46288</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38357,7 +38357,7 @@
         <v>46045</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>46288</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>46289</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>46288</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>46288</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>46288</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>46252</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>46035</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38956,7 +38956,7 @@
         <v>46290</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39029,7 +39029,7 @@
         <v>46294</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39102,7 +39102,7 @@
         <v>46294</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>46238</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>46238</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39321,7 +39321,7 @@
         <v>46295</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>46238</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>46295</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>46295</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39623,7 +39623,7 @@
         <v>46093</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
         <v>46297</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>46203</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>46286</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>46301</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40003,7 +40003,7 @@
         <v>46301</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40081,7 +40081,7 @@
         <v>46301</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>46301</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>46301</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>46301</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>45833</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40461,7 +40461,7 @@
         <v>46303</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40539,7 +40539,7 @@
         <v>45916</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>45308</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>46303</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40763,7 +40763,7 @@
         <v>46189</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>46091</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40909,7 +40909,7 @@
         <v>45833</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>45951</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41060,7 +41060,7 @@
         <v>44223</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41133,7 +41133,7 @@
         <v>44865</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41206,7 +41206,7 @@
         <v>45747</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>45888</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41357,7 +41357,7 @@
         <v>45888</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>46008</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>46132</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41576,7 +41576,7 @@
         <v>46177</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>46286</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>

--- a/Översikt ÅTVIDABERG.xlsx
+++ b/Översikt ÅTVIDABERG.xlsx
@@ -601,7 +601,7 @@
         <v>46276</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>45853</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>45785</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46203</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45848</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45713</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>45343</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>45155</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>46154</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>46276</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>45335</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>46029</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>46181</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>46206</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>44778</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>46203</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2673,75 +2673,199 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
+          <t>A 40918-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ÅTVIDABERG</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>11</v>
+      </c>
+      <c r="T18" t="n">
+        <v>15</v>
+      </c>
+      <c r="U18" t="n">
+        <v>15</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Fjällig taggsvamp s.str.
+Gropticka
+Skarp dropptaggsvamp
+Talltita
+Blåmossa
+Grönpyrola
+Mindre märgborre
+Blåsippa
+Linnea
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0561/artfynd/A 40918-2026 artfynd.xlsx", "A 40918-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor/A 40918-2026 karta.png", "A 40918-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor_geotiff/A 40918-2026 georefererad karta.tif", "A 40918-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomål/A 40918-2026 FSC-klagomål.docx", "A 40918-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomålsmail/A 40918-2026 FSC-klagomål mail.docx", "A 40918-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsyn/A 40918-2026 tillsynsbegäran.docx", "A 40918-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsynsmail/A 40918-2026 tillsynsbegäran mail.docx", "A 40918-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0561/fåglar/A 40918-2026 prioriterade fågelarter.docx", "A 40918-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>A 32060-2022</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>44778</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ÅTVIDABERG</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ÅTVIDABERG</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>0.4</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K19" t="n">
         <v>2</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L19" t="n">
         <v>6</v>
       </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>6</v>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>10</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>13</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>9</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Apelsinticka
 Kattfotslav
@@ -2755,120 +2879,120 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/artfynd/A 32060-2022 artfynd.xlsx", "A 32060-2022")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor/A 32060-2022 karta.png", "A 32060-2022")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor_geotiff/A 32060-2022 georefererad karta.tif", "A 32060-2022")</f>
         <v/>
       </c>
-      <c r="Z18">
+      <c r="Z19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/knärot/A 32060-2022 karta knärot.png", "A 32060-2022")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomål/A 32060-2022 FSC-klagomål.docx", "A 32060-2022")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomålsmail/A 32060-2022 FSC-klagomål mail.docx", "A 32060-2022")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsyn/A 32060-2022 tillsynsbegäran.docx", "A 32060-2022")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsynsmail/A 32060-2022 tillsynsbegäran mail.docx", "A 32060-2022")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/fåglar/A 32060-2022 prioriterade fågelarter.docx", "A 32060-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 37646-2026</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D20" s="1" t="n">
         <v>46276</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ÅTVIDABERG</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="E20" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ÅTVIDABERG</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>Kyrkan</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I20" t="n">
         <v>1.9</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K20" t="n">
         <v>6</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>3</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>3</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R20" t="n">
         <v>3</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S20" t="n">
         <v>10</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>11</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>7</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Bredbrämad bastardsvärmare
 Mindre bastardsvärmare
@@ -2882,107 +3006,107 @@
 Majbräken</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/artfynd/A 37646-2026 artfynd.xlsx", "A 37646-2026")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor/A 37646-2026 karta.png", "A 37646-2026")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor_geotiff/A 37646-2026 georefererad karta.tif", "A 37646-2026")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomål/A 37646-2026 FSC-klagomål.docx", "A 37646-2026")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomålsmail/A 37646-2026 FSC-klagomål mail.docx", "A 37646-2026")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsyn/A 37646-2026 tillsynsbegäran.docx", "A 37646-2026")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsynsmail/A 37646-2026 tillsynsbegäran mail.docx", "A 37646-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 698-2026</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
         <v>46029</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ÅTVIDABERG</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E21" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ÅTVIDABERG</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>0.8</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>5</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>3</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M21" t="n">
         <v>2</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>5</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>2</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S21" t="n">
         <v>10</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>18</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>17</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Knärot
@@ -2996,115 +3120,115 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/artfynd/A 698-2026 artfynd.xlsx", "A 698-2026")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor/A 698-2026 karta.png", "A 698-2026")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor_geotiff/A 698-2026 georefererad karta.tif", "A 698-2026")</f>
         <v/>
       </c>
-      <c r="Z20">
+      <c r="Z21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/knärot/A 698-2026 karta knärot.png", "A 698-2026")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomål/A 698-2026 FSC-klagomål.docx", "A 698-2026")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomålsmail/A 698-2026 FSC-klagomål mail.docx", "A 698-2026")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsyn/A 698-2026 tillsynsbegäran.docx", "A 698-2026")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsynsmail/A 698-2026 tillsynsbegäran mail.docx", "A 698-2026")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/fåglar/A 698-2026 prioriterade fågelarter.docx", "A 698-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 680-2026</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
         <v>46029</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ÅTVIDABERG</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
+      <c r="E22" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÅTVIDABERG</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>1.1</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>2</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>5</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>6</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R22" t="n">
         <v>1</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S22" t="n">
         <v>10</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>17</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>17</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Entita
@@ -3118,115 +3242,115 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/artfynd/A 680-2026 artfynd.xlsx", "A 680-2026")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor/A 680-2026 karta.png", "A 680-2026")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor_geotiff/A 680-2026 georefererad karta.tif", "A 680-2026")</f>
         <v/>
       </c>
-      <c r="Z21">
+      <c r="Z22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/knärot/A 680-2026 karta knärot.png", "A 680-2026")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomål/A 680-2026 FSC-klagomål.docx", "A 680-2026")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomålsmail/A 680-2026 FSC-klagomål mail.docx", "A 680-2026")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsyn/A 680-2026 tillsynsbegäran.docx", "A 680-2026")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsynsmail/A 680-2026 tillsynsbegäran mail.docx", "A 680-2026")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/fåglar/A 680-2026 prioriterade fågelarter.docx", "A 680-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>S 182-2025</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="D23" s="1" t="n">
         <v>45678</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÅTVIDABERG</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+      <c r="E23" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÅTVIDABERG</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>5.2</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>8</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>8</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>10</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>12</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U23" t="n">
         <v>1</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Blekticka
 Gammelekslav
@@ -3240,111 +3364,111 @@
 Svavelticka</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/artfynd/S 182-2025 artfynd.xlsx", "S 182-2025")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor/S 182-2025 karta.png", "S 182-2025")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor_geotiff/S 182-2025 georefererad karta.tif", "S 182-2025")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomål/S 182-2025 FSC-klagomål.docx", "S 182-2025")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomålsmail/S 182-2025 FSC-klagomål mail.docx", "S 182-2025")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsyn/S 182-2025 tillsynsbegäran.docx", "S 182-2025")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsynsmail/S 182-2025 tillsynsbegäran mail.docx", "S 182-2025")</f>
         <v/>
       </c>
-      <c r="AE22">
+      <c r="AE23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/fåglar/S 182-2025 prioriterade fågelarter.docx", "S 182-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A 34707-2025</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
         <v>45848</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÅTVIDABERG</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
+      <c r="E24" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ÅTVIDABERG</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>1.2</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K24" t="n">
         <v>3</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L24" t="n">
         <v>2</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>3</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>1</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S24" t="n">
         <v>8</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>16</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>16</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Motaggsvamp
@@ -3356,120 +3480,120 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/artfynd/A 34707-2025 artfynd.xlsx", "A 34707-2025")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor/A 34707-2025 karta.png", "A 34707-2025")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor_geotiff/A 34707-2025 georefererad karta.tif", "A 34707-2025")</f>
         <v/>
       </c>
-      <c r="Z23">
+      <c r="Z24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/knärot/A 34707-2025 karta knärot.png", "A 34707-2025")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomål/A 34707-2025 FSC-klagomål.docx", "A 34707-2025")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomålsmail/A 34707-2025 FSC-klagomål mail.docx", "A 34707-2025")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsyn/A 34707-2025 tillsynsbegäran.docx", "A 34707-2025")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsynsmail/A 34707-2025 tillsynsbegäran mail.docx", "A 34707-2025")</f>
         <v/>
       </c>
-      <c r="AE23">
+      <c r="AE24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/fåglar/A 34707-2025 prioriterade fågelarter.docx", "A 34707-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 11593-2026</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
         <v>46084</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ÅTVIDABERG</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="E25" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ÅTVIDABERG</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>Holmen skog AB</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="I25" t="n">
         <v>1</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J25" t="n">
         <v>4</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L25" t="n">
         <v>4</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>5</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R25" t="n">
         <v>1</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S25" t="n">
         <v>8</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>10</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Hornvaxskinn
@@ -3481,120 +3605,120 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/artfynd/A 11593-2026 artfynd.xlsx", "A 11593-2026")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor/A 11593-2026 karta.png", "A 11593-2026")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor_geotiff/A 11593-2026 georefererad karta.tif", "A 11593-2026")</f>
         <v/>
       </c>
-      <c r="Z24">
+      <c r="Z25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/knärot/A 11593-2026 karta knärot.png", "A 11593-2026")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomål/A 11593-2026 FSC-klagomål.docx", "A 11593-2026")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomålsmail/A 11593-2026 FSC-klagomål mail.docx", "A 11593-2026")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsyn/A 11593-2026 tillsynsbegäran.docx", "A 11593-2026")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsynsmail/A 11593-2026 tillsynsbegäran mail.docx", "A 11593-2026")</f>
         <v/>
       </c>
-      <c r="AE24">
+      <c r="AE25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/fåglar/A 11593-2026 prioriterade fågelarter.docx", "A 11593-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 12068-2026</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
         <v>46086</v>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ÅTVIDABERG</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
+      <c r="E26" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ÅTVIDABERG</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>Holmen skog AB</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="I26" t="n">
         <v>1.7</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J26" t="n">
         <v>6</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>3</v>
       </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>3</v>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>8</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U26" t="n">
         <v>9</v>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Reliktbock
 Talltita
@@ -3606,116 +3730,116 @@
 Trana</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/artfynd/A 12068-2026 artfynd.xlsx", "A 12068-2026")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor/A 12068-2026 karta.png", "A 12068-2026")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor_geotiff/A 12068-2026 georefererad karta.tif", "A 12068-2026")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomål/A 12068-2026 FSC-klagomål.docx", "A 12068-2026")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomålsmail/A 12068-2026 FSC-klagomål mail.docx", "A 12068-2026")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsyn/A 12068-2026 tillsynsbegäran.docx", "A 12068-2026")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsynsmail/A 12068-2026 tillsynsbegäran mail.docx", "A 12068-2026")</f>
         <v/>
       </c>
-      <c r="AE25">
+      <c r="AE26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/fåglar/A 12068-2026 prioriterade fågelarter.docx", "A 12068-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>A 21664-2025</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D26" s="1" t="n">
+      <c r="D27" s="1" t="n">
         <v>45783</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>ÅTVIDABERG</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="E27" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ÅTVIDABERG</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="I27" t="n">
         <v>1.9</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J27" t="n">
         <v>5</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K27" t="n">
         <v>4</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>1</v>
       </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>8</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T27" t="n">
         <v>17</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U27" t="n">
         <v>3</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Kricka
 Dvärghäxört
@@ -3727,111 +3851,111 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/artfynd/A 21664-2025 artfynd.xlsx", "A 21664-2025")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor/A 21664-2025 karta.png", "A 21664-2025")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor_geotiff/A 21664-2025 georefererad karta.tif", "A 21664-2025")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomål/A 21664-2025 FSC-klagomål.docx", "A 21664-2025")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomålsmail/A 21664-2025 FSC-klagomål mail.docx", "A 21664-2025")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsyn/A 21664-2025 tillsynsbegäran.docx", "A 21664-2025")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsynsmail/A 21664-2025 tillsynsbegäran mail.docx", "A 21664-2025")</f>
         <v/>
       </c>
-      <c r="AE26">
+      <c r="AE27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/fåglar/A 21664-2025 prioriterade fågelarter.docx", "A 21664-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>S 5294-2021</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
-      <c r="D27" s="1" t="n">
+      <c r="D28" s="1" t="n">
         <v>44426</v>
       </c>
-      <c r="E27" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>ÅTVIDABERG</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
+      <c r="E28" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ÅTVIDABERG</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>2.4</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J28" t="n">
         <v>2</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K28" t="n">
         <v>5</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M28" t="n">
         <v>1</v>
       </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
         <v>2</v>
       </c>
-      <c r="R27" t="n">
+      <c r="R28" t="n">
         <v>1</v>
       </c>
-      <c r="S27" t="n">
+      <c r="S28" t="n">
         <v>8</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T28" t="n">
         <v>8</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U28" t="n">
         <v>2</v>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Grynig filtlav
@@ -3843,116 +3967,116 @@
 Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/artfynd/S 5294-2021 artfynd.xlsx", "S 5294-2021")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor/S 5294-2021 karta.png", "S 5294-2021")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor_geotiff/S 5294-2021 georefererad karta.tif", "S 5294-2021")</f>
         <v/>
       </c>
-      <c r="Z27">
+      <c r="Z28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/knärot/S 5294-2021 karta knärot.png", "S 5294-2021")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomål/S 5294-2021 FSC-klagomål.docx", "S 5294-2021")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomålsmail/S 5294-2021 FSC-klagomål mail.docx", "S 5294-2021")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsyn/S 5294-2021 tillsynsbegäran.docx", "S 5294-2021")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsynsmail/S 5294-2021 tillsynsbegäran mail.docx", "S 5294-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>S 1420-2025</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D28" s="1" t="n">
+      <c r="D29" s="1" t="n">
         <v>45783</v>
       </c>
-      <c r="E28" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ÅTVIDABERG</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="E29" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ÅTVIDABERG</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I28" t="n">
+      <c r="I29" t="n">
         <v>1.9</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J29" t="n">
         <v>5</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K29" t="n">
         <v>4</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L29" t="n">
         <v>1</v>
       </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
         <v>1</v>
       </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>8</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T29" t="n">
         <v>17</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U29" t="n">
         <v>3</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Kricka
 Dvärghäxört
@@ -3964,111 +4088,111 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/artfynd/S 1420-2025 artfynd.xlsx", "S 1420-2025")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor/S 1420-2025 karta.png", "S 1420-2025")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor_geotiff/S 1420-2025 georefererad karta.tif", "S 1420-2025")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomål/S 1420-2025 FSC-klagomål.docx", "S 1420-2025")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomålsmail/S 1420-2025 FSC-klagomål mail.docx", "S 1420-2025")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsyn/S 1420-2025 tillsynsbegäran.docx", "S 1420-2025")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsynsmail/S 1420-2025 tillsynsbegäran mail.docx", "S 1420-2025")</f>
         <v/>
       </c>
-      <c r="AE28">
+      <c r="AE29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/fåglar/S 1420-2025 prioriterade fågelarter.docx", "S 1420-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>A 3380-2023</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
         <v>44949</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ÅTVIDABERG</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
+      <c r="E30" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ÅTVIDABERG</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>1.9</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J30" t="n">
         <v>6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K30" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M30" t="n">
         <v>1</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>2</v>
       </c>
-      <c r="R29" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S30" t="n">
         <v>7</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T30" t="n">
         <v>19</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U30" t="n">
         <v>19</v>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Talltita
@@ -4079,115 +4203,115 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/artfynd/A 3380-2023 artfynd.xlsx", "A 3380-2023")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor/A 3380-2023 karta.png", "A 3380-2023")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor_geotiff/A 3380-2023 georefererad karta.tif", "A 3380-2023")</f>
         <v/>
       </c>
-      <c r="Z29">
+      <c r="Z30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/knärot/A 3380-2023 karta knärot.png", "A 3380-2023")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomål/A 3380-2023 FSC-klagomål.docx", "A 3380-2023")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomålsmail/A 3380-2023 FSC-klagomål mail.docx", "A 3380-2023")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsyn/A 3380-2023 tillsynsbegäran.docx", "A 3380-2023")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsynsmail/A 3380-2023 tillsynsbegäran mail.docx", "A 3380-2023")</f>
         <v/>
       </c>
-      <c r="AE29">
+      <c r="AE30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/fåglar/A 3380-2023 prioriterade fågelarter.docx", "A 3380-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>A 22412-2026</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
         <v>46154</v>
       </c>
-      <c r="E30" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ÅTVIDABERG</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
+      <c r="E31" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ÅTVIDABERG</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
         <v>11</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J31" t="n">
         <v>3</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K31" t="n">
         <v>3</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
         <v>1</v>
       </c>
-      <c r="R30" t="n">
+      <c r="R31" t="n">
         <v>1</v>
       </c>
-      <c r="S30" t="n">
+      <c r="S31" t="n">
         <v>7</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T31" t="n">
         <v>11</v>
       </c>
-      <c r="U30" t="n">
+      <c r="U31" t="n">
         <v>11</v>
       </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Björksplintborre
@@ -4198,120 +4322,120 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/artfynd/A 22412-2026 artfynd.xlsx", "A 22412-2026")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor/A 22412-2026 karta.png", "A 22412-2026")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor_geotiff/A 22412-2026 georefererad karta.tif", "A 22412-2026")</f>
         <v/>
       </c>
-      <c r="Z30">
+      <c r="Z31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/knärot/A 22412-2026 karta knärot.png", "A 22412-2026")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomål/A 22412-2026 FSC-klagomål.docx", "A 22412-2026")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomålsmail/A 22412-2026 FSC-klagomål mail.docx", "A 22412-2026")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsyn/A 22412-2026 tillsynsbegäran.docx", "A 22412-2026")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsynsmail/A 22412-2026 tillsynsbegäran mail.docx", "A 22412-2026")</f>
         <v/>
       </c>
-      <c r="AE30">
+      <c r="AE31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/fåglar/A 22412-2026 prioriterade fågelarter.docx", "A 22412-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>A 11738-2026</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
         <v>46084</v>
       </c>
-      <c r="E31" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ÅTVIDABERG</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="E32" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ÅTVIDABERG</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>Holmen skog AB</t>
         </is>
       </c>
-      <c r="I31" t="n">
+      <c r="I32" t="n">
         <v>1.6</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J32" t="n">
         <v>2</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K32" t="n">
         <v>2</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M32" t="n">
         <v>1</v>
       </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
         <v>4</v>
       </c>
-      <c r="R31" t="n">
+      <c r="R32" t="n">
         <v>1</v>
       </c>
-      <c r="S31" t="n">
+      <c r="S32" t="n">
         <v>7</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T32" t="n">
         <v>12</v>
       </c>
-      <c r="U31" t="n">
+      <c r="U32" t="n">
         <v>12</v>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Dvärgbägarlav
@@ -4322,115 +4446,115 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W31">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/artfynd/A 11738-2026 artfynd.xlsx", "A 11738-2026")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor/A 11738-2026 karta.png", "A 11738-2026")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor_geotiff/A 11738-2026 georefererad karta.tif", "A 11738-2026")</f>
         <v/>
       </c>
-      <c r="Z31">
+      <c r="Z32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/knärot/A 11738-2026 karta knärot.png", "A 11738-2026")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomål/A 11738-2026 FSC-klagomål.docx", "A 11738-2026")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomålsmail/A 11738-2026 FSC-klagomål mail.docx", "A 11738-2026")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsyn/A 11738-2026 tillsynsbegäran.docx", "A 11738-2026")</f>
         <v/>
       </c>
-      <c r="AD31">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsynsmail/A 11738-2026 tillsynsbegäran mail.docx", "A 11738-2026")</f>
         <v/>
       </c>
-      <c r="AE31">
+      <c r="AE32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/fåglar/A 11738-2026 prioriterade fågelarter.docx", "A 11738-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>A 614-2024</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
         <v>45299</v>
       </c>
-      <c r="E32" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>ÅTVIDABERG</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
+      <c r="E33" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ÅTVIDABERG</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
         <v>3.9</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J33" t="n">
         <v>3</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K33" t="n">
         <v>1</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L33" t="n">
         <v>3</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M33" t="n">
         <v>2</v>
       </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>5</v>
       </c>
-      <c r="R32" t="n">
+      <c r="R33" t="n">
         <v>2</v>
       </c>
-      <c r="S32" t="n">
+      <c r="S33" t="n">
         <v>7</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T33" t="n">
         <v>16</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U33" t="n">
         <v>7</v>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -4441,115 +4565,115 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/artfynd/A 614-2024 artfynd.xlsx", "A 614-2024")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor/A 614-2024 karta.png", "A 614-2024")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor_geotiff/A 614-2024 georefererad karta.tif", "A 614-2024")</f>
         <v/>
       </c>
-      <c r="Z32">
+      <c r="Z33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/knärot/A 614-2024 karta knärot.png", "A 614-2024")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomål/A 614-2024 FSC-klagomål.docx", "A 614-2024")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomålsmail/A 614-2024 FSC-klagomål mail.docx", "A 614-2024")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsyn/A 614-2024 tillsynsbegäran.docx", "A 614-2024")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsynsmail/A 614-2024 tillsynsbegäran mail.docx", "A 614-2024")</f>
         <v/>
       </c>
-      <c r="AE32">
+      <c r="AE33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/fåglar/A 614-2024 prioriterade fågelarter.docx", "A 614-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A 34605-2022</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
         <v>44795</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>ÅTVIDABERG</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
+      <c r="E34" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ÅTVIDABERG</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>0.8</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J34" t="n">
         <v>2</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M34" t="n">
         <v>1</v>
       </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>5</v>
       </c>
-      <c r="R33" t="n">
+      <c r="R34" t="n">
         <v>1</v>
       </c>
-      <c r="S33" t="n">
+      <c r="S34" t="n">
         <v>6</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T34" t="n">
         <v>7</v>
       </c>
-      <c r="U33" t="n">
+      <c r="U34" t="n">
         <v>2</v>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Hängticka
@@ -4559,116 +4683,116 @@
 Tofsmes</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/artfynd/A 34605-2022 artfynd.xlsx", "A 34605-2022")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor/A 34605-2022 karta.png", "A 34605-2022")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor_geotiff/A 34605-2022 georefererad karta.tif", "A 34605-2022")</f>
         <v/>
       </c>
-      <c r="Z33">
+      <c r="Z34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/knärot/A 34605-2022 karta knärot.png", "A 34605-2022")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomål/A 34605-2022 FSC-klagomål.docx", "A 34605-2022")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomålsmail/A 34605-2022 FSC-klagomål mail.docx", "A 34605-2022")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsyn/A 34605-2022 tillsynsbegäran.docx", "A 34605-2022")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsynsmail/A 34605-2022 tillsynsbegäran mail.docx", "A 34605-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>A 40628-2025</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="n">
         <v>45896</v>
       </c>
-      <c r="E34" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>ÅTVIDABERG</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
+      <c r="E35" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ÅTVIDABERG</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I34" t="n">
+      <c r="I35" t="n">
         <v>1.8</v>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
         <v>1</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L35" t="n">
         <v>5</v>
       </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
         <v>5</v>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>6</v>
       </c>
-      <c r="T34" t="n">
+      <c r="T35" t="n">
         <v>8</v>
       </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Dvärgbägarlav
 Hornvaxskinn
@@ -4678,147 +4802,32 @@
 Vedticka</t>
         </is>
       </c>
-      <c r="W34">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/artfynd/A 40628-2025 artfynd.xlsx", "A 40628-2025")</f>
         <v/>
       </c>
-      <c r="X34">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor/A 40628-2025 karta.png", "A 40628-2025")</f>
         <v/>
       </c>
-      <c r="Y34">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor_geotiff/A 40628-2025 georefererad karta.tif", "A 40628-2025")</f>
         <v/>
       </c>
-      <c r="AA34">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomål/A 40628-2025 FSC-klagomål.docx", "A 40628-2025")</f>
         <v/>
       </c>
-      <c r="AB34">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomålsmail/A 40628-2025 FSC-klagomål mail.docx", "A 40628-2025")</f>
         <v/>
       </c>
-      <c r="AC34">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsyn/A 40628-2025 tillsynsbegäran.docx", "A 40628-2025")</f>
         <v/>
       </c>
-      <c r="AD34">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsynsmail/A 40628-2025 tillsynsbegäran mail.docx", "A 40628-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A 40918-2026</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>ÅTVIDABERG</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>3</v>
-      </c>
-      <c r="L35" t="n">
-        <v>3</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>3</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>6</v>
-      </c>
-      <c r="T35" t="n">
-        <v>8</v>
-      </c>
-      <c r="U35" t="n">
-        <v>8</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Fjällig taggsvamp s.str.
-Gropticka
-Blåmossa
-Grönpyrola
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0561/artfynd/A 40918-2026 artfynd.xlsx", "A 40918-2026")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor/A 40918-2026 karta.png", "A 40918-2026")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0561/kartor_geotiff/A 40918-2026 georefererad karta.tif", "A 40918-2026")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomål/A 40918-2026 FSC-klagomål.docx", "A 40918-2026")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0561/klagomålsmail/A 40918-2026 FSC-klagomål mail.docx", "A 40918-2026")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsyn/A 40918-2026 tillsynsbegäran.docx", "A 40918-2026")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0561/tillsynsmail/A 40918-2026 tillsynsbegäran mail.docx", "A 40918-2026")</f>
         <v/>
       </c>
     </row>
@@ -4842,7 +4851,7 @@
         <v>44546</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4956,7 +4965,7 @@
         <v>44841</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5078,7 +5087,7 @@
         <v>45156</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5195,7 +5204,7 @@
         <v>44823</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5304,7 +5313,7 @@
         <v>45156</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5421,7 +5430,7 @@
         <v>46279</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5535,7 +5544,7 @@
         <v>44952</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5648,7 +5657,7 @@
         <v>45896</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5761,7 +5770,7 @@
         <v>46084</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5882,7 +5891,7 @@
         <v>44778</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5998,7 +6007,7 @@
         <v>44516</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6110,7 +6119,7 @@
         <v>45259</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6217,7 +6226,7 @@
         <v>44964</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6324,7 +6333,7 @@
         <v>44789</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6431,7 +6440,7 @@
         <v>46279</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6547,7 +6556,7 @@
         <v>44789</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6653,7 +6662,7 @@
         <v>44874</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6768,7 +6777,7 @@
         <v>44631</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6874,7 +6883,7 @@
         <v>45274</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6985,7 +6994,7 @@
         <v>45896</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7096,7 +7105,7 @@
         <v>45131</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7202,7 +7211,7 @@
         <v>45938</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7313,7 +7322,7 @@
         <v>44777</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7419,7 +7428,7 @@
         <v>46112</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7530,7 +7539,7 @@
         <v>45666</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7640,7 +7649,7 @@
         <v>45111</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7751,7 +7760,7 @@
         <v>46219</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7862,7 +7871,7 @@
         <v>46279</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7973,7 +7982,7 @@
         <v>45758</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8083,7 +8092,7 @@
         <v>44789</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8188,7 +8197,7 @@
         <v>44851</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8293,7 +8302,7 @@
         <v>44621</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8398,7 +8407,7 @@
         <v>44609</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8503,7 +8512,7 @@
         <v>45072</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8613,7 +8622,7 @@
         <v>44942</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8718,7 +8727,7 @@
         <v>44935</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8823,7 +8832,7 @@
         <v>45072</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8933,7 +8942,7 @@
         <v>45982</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9042,7 +9051,7 @@
         <v>45323</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9147,7 +9156,7 @@
         <v>44994</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9257,7 +9266,7 @@
         <v>45565</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9367,7 +9376,7 @@
         <v>45938</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9476,7 +9485,7 @@
         <v>45323</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9585,7 +9594,7 @@
         <v>46154</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9690,7 +9699,7 @@
         <v>45979</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9800,7 +9809,7 @@
         <v>45204</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9905,7 +9914,7 @@
         <v>45222</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10010,7 +10019,7 @@
         <v>46048</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10115,7 +10124,7 @@
         <v>46084</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10229,7 +10238,7 @@
         <v>46112</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10343,7 +10352,7 @@
         <v>44862</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10453,7 +10462,7 @@
         <v>45042</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10558,7 +10567,7 @@
         <v>45379</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10663,7 +10672,7 @@
         <v>45727</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10768,7 +10777,7 @@
         <v>46286</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10873,7 +10882,7 @@
         <v>45468</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10978,7 +10987,7 @@
         <v>45323</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11083,7 +11092,7 @@
         <v>46301</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11193,7 +11202,7 @@
         <v>45662</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11298,7 +11307,7 @@
         <v>44582</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11371,7 +11380,7 @@
         <v>44641</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11444,7 +11453,7 @@
         <v>44826</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11517,7 +11526,7 @@
         <v>44539</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11590,7 +11599,7 @@
         <v>44546</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11668,7 +11677,7 @@
         <v>44827</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11741,7 +11750,7 @@
         <v>44573</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11814,7 +11823,7 @@
         <v>44495</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11892,7 +11901,7 @@
         <v>44782</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11965,7 +11974,7 @@
         <v>44831</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12038,7 +12047,7 @@
         <v>44586</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12111,7 +12120,7 @@
         <v>44729</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12189,7 +12198,7 @@
         <v>44543</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12262,7 +12271,7 @@
         <v>44552</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12340,7 +12349,7 @@
         <v>44531</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12418,7 +12427,7 @@
         <v>44573</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12491,7 +12500,7 @@
         <v>44593</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12564,7 +12573,7 @@
         <v>44539</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12637,7 +12646,7 @@
         <v>44838</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12710,7 +12719,7 @@
         <v>44789</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12783,7 +12792,7 @@
         <v>44627</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12856,7 +12865,7 @@
         <v>44706</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12929,7 +12938,7 @@
         <v>44789</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13002,7 +13011,7 @@
         <v>44830</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13075,7 +13084,7 @@
         <v>44767</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13148,7 +13157,7 @@
         <v>44735</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13221,7 +13230,7 @@
         <v>44683</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13294,7 +13303,7 @@
         <v>44724</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13367,7 +13376,7 @@
         <v>44784</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13440,7 +13449,7 @@
         <v>44732</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13518,7 +13527,7 @@
         <v>44860</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13596,7 +13605,7 @@
         <v>44514</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13669,7 +13678,7 @@
         <v>44545</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13742,7 +13751,7 @@
         <v>44729</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13820,7 +13829,7 @@
         <v>44760</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13893,7 +13902,7 @@
         <v>44778</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13966,7 +13975,7 @@
         <v>44778</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14039,7 +14048,7 @@
         <v>44629</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14112,7 +14121,7 @@
         <v>44888</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14185,7 +14194,7 @@
         <v>44967</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14258,7 +14267,7 @@
         <v>44831</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14331,7 +14340,7 @@
         <v>45362</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14409,7 +14418,7 @@
         <v>44991</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14482,7 +14491,7 @@
         <v>44973</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14555,7 +14564,7 @@
         <v>44895</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14628,7 +14637,7 @@
         <v>44579</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14701,7 +14710,7 @@
         <v>44847</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14779,7 +14788,7 @@
         <v>44949</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14852,7 +14861,7 @@
         <v>45548</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14925,7 +14934,7 @@
         <v>45440</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14998,7 +15007,7 @@
         <v>44494</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15076,7 +15085,7 @@
         <v>44621</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15149,7 +15158,7 @@
         <v>44745</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15222,7 +15231,7 @@
         <v>45222</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15295,7 +15304,7 @@
         <v>45114</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15368,7 +15377,7 @@
         <v>45077</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15441,7 +15450,7 @@
         <v>44742</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15514,7 +15523,7 @@
         <v>45036</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15587,7 +15596,7 @@
         <v>44806</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15660,7 +15669,7 @@
         <v>45167</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15733,7 +15742,7 @@
         <v>45665</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15806,7 +15815,7 @@
         <v>45348</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15879,7 +15888,7 @@
         <v>45113</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15957,7 +15966,7 @@
         <v>44777</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16030,7 +16039,7 @@
         <v>45301</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16103,7 +16112,7 @@
         <v>45415</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16176,7 +16185,7 @@
         <v>44516</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16254,7 +16263,7 @@
         <v>44778</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16327,7 +16336,7 @@
         <v>45089</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16400,7 +16409,7 @@
         <v>45534</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16473,7 +16482,7 @@
         <v>45664</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16546,7 +16555,7 @@
         <v>44770</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16619,7 +16628,7 @@
         <v>44607</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16692,7 +16701,7 @@
         <v>45362</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16770,7 +16779,7 @@
         <v>45180</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16843,7 +16852,7 @@
         <v>44897</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16916,7 +16925,7 @@
         <v>44622</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16989,7 +16998,7 @@
         <v>45187</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17067,7 +17076,7 @@
         <v>45229</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17140,7 +17149,7 @@
         <v>45475</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17213,7 +17222,7 @@
         <v>45224</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17291,7 +17300,7 @@
         <v>45323</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17364,7 +17373,7 @@
         <v>45229</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17437,7 +17446,7 @@
         <v>45229</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17510,7 +17519,7 @@
         <v>45433</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17583,7 +17592,7 @@
         <v>45122</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17656,7 +17665,7 @@
         <v>45259</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17729,7 +17738,7 @@
         <v>45259</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17802,7 +17811,7 @@
         <v>44767</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17875,7 +17884,7 @@
         <v>45924</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17948,7 +17957,7 @@
         <v>45758</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18021,7 +18030,7 @@
         <v>44721</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18094,7 +18103,7 @@
         <v>45334</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18167,7 +18176,7 @@
         <v>44767</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18240,7 +18249,7 @@
         <v>45358</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18313,7 +18322,7 @@
         <v>45217</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18386,7 +18395,7 @@
         <v>45665</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18459,7 +18468,7 @@
         <v>45072</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18532,7 +18541,7 @@
         <v>45824</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18605,7 +18614,7 @@
         <v>45727</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18678,7 +18687,7 @@
         <v>45740</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18751,7 +18760,7 @@
         <v>45896</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18829,7 +18838,7 @@
         <v>45896</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18907,7 +18916,7 @@
         <v>45608</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18985,7 +18994,7 @@
         <v>45608</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19063,7 +19072,7 @@
         <v>44937</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19136,7 +19145,7 @@
         <v>45205</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19214,7 +19223,7 @@
         <v>44876</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19287,7 +19296,7 @@
         <v>45077</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19360,7 +19369,7 @@
         <v>44935</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19433,7 +19442,7 @@
         <v>45835</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19506,7 +19515,7 @@
         <v>45343</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19579,7 +19588,7 @@
         <v>45736</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19652,7 +19661,7 @@
         <v>45601</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19725,7 +19734,7 @@
         <v>45707</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19798,7 +19807,7 @@
         <v>45917</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19871,7 +19880,7 @@
         <v>45916</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19944,7 +19953,7 @@
         <v>44988</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20022,7 +20031,7 @@
         <v>45695</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20095,7 +20104,7 @@
         <v>45169</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20168,7 +20177,7 @@
         <v>44872</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20246,7 +20255,7 @@
         <v>45923</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20319,7 +20328,7 @@
         <v>45685</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20392,7 +20401,7 @@
         <v>44812</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20465,7 +20474,7 @@
         <v>44574</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20538,7 +20547,7 @@
         <v>45104</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20611,7 +20620,7 @@
         <v>45104</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20684,7 +20693,7 @@
         <v>44833</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20757,7 +20766,7 @@
         <v>45932</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20830,7 +20839,7 @@
         <v>45168</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20908,7 +20917,7 @@
         <v>45939</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20981,7 +20990,7 @@
         <v>45022</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21054,7 +21063,7 @@
         <v>45946</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21132,7 +21141,7 @@
         <v>44938</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21205,7 +21214,7 @@
         <v>45946</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21283,7 +21292,7 @@
         <v>45951</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21356,7 +21365,7 @@
         <v>45817</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21429,7 +21438,7 @@
         <v>46154</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21502,7 +21511,7 @@
         <v>45954</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21580,7 +21589,7 @@
         <v>46154</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21653,7 +21662,7 @@
         <v>44791</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21726,7 +21735,7 @@
         <v>44938</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21799,7 +21808,7 @@
         <v>46156</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21872,7 +21881,7 @@
         <v>45229</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21945,7 +21954,7 @@
         <v>45839</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22018,7 +22027,7 @@
         <v>44988</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22091,7 +22100,7 @@
         <v>45296</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22164,7 +22173,7 @@
         <v>45384</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22237,7 +22246,7 @@
         <v>44586</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22310,7 +22319,7 @@
         <v>45176</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22383,7 +22392,7 @@
         <v>45740</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22456,7 +22465,7 @@
         <v>45415</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22529,7 +22538,7 @@
         <v>45118</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22602,7 +22611,7 @@
         <v>45187</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22675,7 +22684,7 @@
         <v>46167</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22748,7 +22757,7 @@
         <v>45982</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22821,7 +22830,7 @@
         <v>45982</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22894,7 +22903,7 @@
         <v>45415</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22967,7 +22976,7 @@
         <v>44851</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23040,7 +23049,7 @@
         <v>44777</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23113,7 +23122,7 @@
         <v>45217</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23186,7 +23195,7 @@
         <v>44565</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23259,7 +23268,7 @@
         <v>44545</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23332,7 +23341,7 @@
         <v>44517</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23405,7 +23414,7 @@
         <v>44938</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23478,7 +23487,7 @@
         <v>45040</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23551,7 +23560,7 @@
         <v>44980</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23624,7 +23633,7 @@
         <v>45107</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23697,7 +23706,7 @@
         <v>44942</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23770,7 +23779,7 @@
         <v>45440</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23843,7 +23852,7 @@
         <v>45092</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23916,7 +23925,7 @@
         <v>46171</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23989,7 +23998,7 @@
         <v>45379</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24062,7 +24071,7 @@
         <v>45747</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24140,7 +24149,7 @@
         <v>44516</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24218,7 +24227,7 @@
         <v>45315</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24291,7 +24300,7 @@
         <v>44546</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24369,7 +24378,7 @@
         <v>45250</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24447,7 +24456,7 @@
         <v>45308</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24520,7 +24529,7 @@
         <v>45554</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24593,7 +24602,7 @@
         <v>45267</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24666,7 +24675,7 @@
         <v>44721</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24739,7 +24748,7 @@
         <v>44995</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24817,7 +24826,7 @@
         <v>44721</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24890,7 +24899,7 @@
         <v>45208</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24968,7 +24977,7 @@
         <v>46034</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25041,7 +25050,7 @@
         <v>44964</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25114,7 +25123,7 @@
         <v>46035</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25187,7 +25196,7 @@
         <v>46178</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25260,7 +25269,7 @@
         <v>46178</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25333,7 +25342,7 @@
         <v>45457</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25411,7 +25420,7 @@
         <v>46178</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25484,7 +25493,7 @@
         <v>46043</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25562,7 +25571,7 @@
         <v>46043</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25635,7 +25644,7 @@
         <v>46043</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25713,7 +25722,7 @@
         <v>46043</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25791,7 +25800,7 @@
         <v>46043</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25864,7 +25873,7 @@
         <v>46043</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25937,7 +25946,7 @@
         <v>46045</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26015,7 +26024,7 @@
         <v>45440</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26088,7 +26097,7 @@
         <v>46045</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26166,7 +26175,7 @@
         <v>44833</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26239,7 +26248,7 @@
         <v>46045</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26317,7 +26326,7 @@
         <v>46049</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26390,7 +26399,7 @@
         <v>46048</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26463,7 +26472,7 @@
         <v>46050</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26536,7 +26545,7 @@
         <v>46050</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26609,7 +26618,7 @@
         <v>46055</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26687,7 +26696,7 @@
         <v>46055</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26765,7 +26774,7 @@
         <v>46055</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26843,7 +26852,7 @@
         <v>46034</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26916,7 +26925,7 @@
         <v>44735</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26989,7 +26998,7 @@
         <v>46070</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27067,7 +27076,7 @@
         <v>44741</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27140,7 +27149,7 @@
         <v>46185</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27213,7 +27222,7 @@
         <v>46083</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27291,7 +27300,7 @@
         <v>46086</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27369,7 +27378,7 @@
         <v>46085</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27442,7 +27451,7 @@
         <v>46189</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27515,7 +27524,7 @@
         <v>44881</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27588,7 +27597,7 @@
         <v>46092</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27661,7 +27670,7 @@
         <v>44931</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27734,7 +27743,7 @@
         <v>46097</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27807,7 +27816,7 @@
         <v>46099</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27880,7 +27889,7 @@
         <v>44489</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27958,7 +27967,7 @@
         <v>44806</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28031,7 +28040,7 @@
         <v>45097</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28104,7 +28113,7 @@
         <v>46195</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28177,7 +28186,7 @@
         <v>45155</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28250,7 +28259,7 @@
         <v>45104</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28328,7 +28337,7 @@
         <v>45442</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28401,7 +28410,7 @@
         <v>45378</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28474,7 +28483,7 @@
         <v>45483</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28547,7 +28556,7 @@
         <v>44972</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28620,7 +28629,7 @@
         <v>46203</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28698,7 +28707,7 @@
         <v>46204</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28776,7 +28785,7 @@
         <v>45666</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28849,7 +28858,7 @@
         <v>45572</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28922,7 +28931,7 @@
         <v>45827</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28995,7 +29004,7 @@
         <v>45796</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29068,7 +29077,7 @@
         <v>46203</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29146,7 +29155,7 @@
         <v>45555</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29219,7 +29228,7 @@
         <v>45784</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29292,7 +29301,7 @@
         <v>44970</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29365,7 +29374,7 @@
         <v>45538</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29438,7 +29447,7 @@
         <v>44930</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29511,7 +29520,7 @@
         <v>45090</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29584,7 +29593,7 @@
         <v>44495</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29662,7 +29671,7 @@
         <v>45098</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29735,7 +29744,7 @@
         <v>45098</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29808,7 +29817,7 @@
         <v>45063</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29886,7 +29895,7 @@
         <v>45243</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29959,7 +29968,7 @@
         <v>45334</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30032,7 +30041,7 @@
         <v>45243</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30105,7 +30114,7 @@
         <v>45022</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30178,7 +30187,7 @@
         <v>44902</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30251,7 +30260,7 @@
         <v>46044</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30324,7 +30333,7 @@
         <v>45225</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30397,7 +30406,7 @@
         <v>44922</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30470,7 +30479,7 @@
         <v>44631</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30543,7 +30552,7 @@
         <v>44917</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30616,7 +30625,7 @@
         <v>45097</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30689,7 +30698,7 @@
         <v>45224</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30762,7 +30771,7 @@
         <v>44618</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30835,7 +30844,7 @@
         <v>44742</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30908,7 +30917,7 @@
         <v>45387</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30981,7 +30990,7 @@
         <v>45122</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31054,7 +31063,7 @@
         <v>44745</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31127,7 +31136,7 @@
         <v>45183</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31200,7 +31209,7 @@
         <v>45400</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31273,7 +31282,7 @@
         <v>46279</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31351,7 +31360,7 @@
         <v>44965</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31424,7 +31433,7 @@
         <v>45471</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31497,7 +31506,7 @@
         <v>46279</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31575,7 +31584,7 @@
         <v>46279</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31653,7 +31662,7 @@
         <v>46279</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31731,7 +31740,7 @@
         <v>46279</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31809,7 +31818,7 @@
         <v>44817</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31882,7 +31891,7 @@
         <v>45328</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31955,7 +31964,7 @@
         <v>46281</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32028,7 +32037,7 @@
         <v>46280</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32101,7 +32110,7 @@
         <v>45597</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32174,7 +32183,7 @@
         <v>45225</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32247,7 +32256,7 @@
         <v>46239</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32320,7 +32329,7 @@
         <v>46281</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32393,7 +32402,7 @@
         <v>46281</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32466,7 +32475,7 @@
         <v>46239</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32539,7 +32548,7 @@
         <v>46239</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32612,7 +32621,7 @@
         <v>46238</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32685,7 +32694,7 @@
         <v>46239</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32758,7 +32767,7 @@
         <v>45379</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32831,7 +32840,7 @@
         <v>45379</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32904,7 +32913,7 @@
         <v>45112</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32982,7 +32991,7 @@
         <v>45184</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33055,7 +33064,7 @@
         <v>45316</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33128,7 +33137,7 @@
         <v>44564</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33201,7 +33210,7 @@
         <v>46286</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33274,7 +33283,7 @@
         <v>46286</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33347,7 +33356,7 @@
         <v>45182</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33420,7 +33429,7 @@
         <v>46084</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33498,7 +33507,7 @@
         <v>46286</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33571,7 +33580,7 @@
         <v>46286</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33644,7 +33653,7 @@
         <v>46244</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33717,7 +33726,7 @@
         <v>46286</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33790,7 +33799,7 @@
         <v>45334</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33863,7 +33872,7 @@
         <v>46244</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33936,7 +33945,7 @@
         <v>46029</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34009,7 +34018,7 @@
         <v>46244</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34082,7 +34091,7 @@
         <v>46287</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34155,7 +34164,7 @@
         <v>46244</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34228,7 +34237,7 @@
         <v>44839</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34301,7 +34310,7 @@
         <v>46288</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34374,7 +34383,7 @@
         <v>46288</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34447,7 +34456,7 @@
         <v>46288</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34525,7 +34534,7 @@
         <v>44784</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34598,7 +34607,7 @@
         <v>45258</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34676,7 +34685,7 @@
         <v>46288</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34749,7 +34758,7 @@
         <v>46288</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34822,7 +34831,7 @@
         <v>46289</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34895,7 +34904,7 @@
         <v>45384</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34968,7 +34977,7 @@
         <v>46288</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35041,7 +35050,7 @@
         <v>46288</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35119,7 +35128,7 @@
         <v>46288</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35192,7 +35201,7 @@
         <v>46288</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35270,7 +35279,7 @@
         <v>45763</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35343,7 +35352,7 @@
         <v>45040</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35416,7 +35425,7 @@
         <v>45169</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35489,7 +35498,7 @@
         <v>46035</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35562,7 +35571,7 @@
         <v>46289</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35635,7 +35644,7 @@
         <v>44596</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35708,7 +35717,7 @@
         <v>46290</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35781,7 +35790,7 @@
         <v>45296</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35854,7 +35863,7 @@
         <v>45720</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35927,7 +35936,7 @@
         <v>46045</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36005,7 +36014,7 @@
         <v>46195</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36078,7 +36087,7 @@
         <v>45308</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36151,7 +36160,7 @@
         <v>46295</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36224,7 +36233,7 @@
         <v>44902</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36297,7 +36306,7 @@
         <v>45525</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36370,7 +36379,7 @@
         <v>45715</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36448,7 +36457,7 @@
         <v>46294</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36521,7 +36530,7 @@
         <v>46294</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36594,7 +36603,7 @@
         <v>45168</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36667,7 +36676,7 @@
         <v>45153</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36740,7 +36749,7 @@
         <v>45180</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36813,7 +36822,7 @@
         <v>45182</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36886,7 +36895,7 @@
         <v>44582</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36959,7 +36968,7 @@
         <v>45415</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37032,7 +37041,7 @@
         <v>44546</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37110,7 +37119,7 @@
         <v>46252</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37183,7 +37192,7 @@
         <v>44915</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37256,7 +37265,7 @@
         <v>46093</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37329,7 +37338,7 @@
         <v>46203</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37407,7 +37416,7 @@
         <v>45296</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37480,7 +37489,7 @@
         <v>46295</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37558,7 +37567,7 @@
         <v>45261</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37631,7 +37640,7 @@
         <v>44656</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37704,7 +37713,7 @@
         <v>46295</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37782,7 +37791,7 @@
         <v>46286</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37855,7 +37864,7 @@
         <v>46301</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37933,7 +37942,7 @@
         <v>46301</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38006,7 +38015,7 @@
         <v>46301</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38084,7 +38093,7 @@
         <v>45707</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38157,7 +38166,7 @@
         <v>46301</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38235,7 +38244,7 @@
         <v>46301</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38308,7 +38317,7 @@
         <v>46301</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38386,7 +38395,7 @@
         <v>45784</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38459,7 +38468,7 @@
         <v>46189</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38532,7 +38541,7 @@
         <v>45916</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38610,7 +38619,7 @@
         <v>46091</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38683,7 +38692,7 @@
         <v>45833</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38761,7 +38770,7 @@
         <v>45833</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38839,7 +38848,7 @@
         <v>45308</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38912,7 +38921,7 @@
         <v>45951</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38985,7 +38994,7 @@
         <v>45796</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39058,7 +39067,7 @@
         <v>45308</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39131,7 +39140,7 @@
         <v>46303</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39204,7 +39213,7 @@
         <v>45671</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39277,7 +39286,7 @@
         <v>45799</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39350,7 +39359,7 @@
         <v>46303</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39428,7 +39437,7 @@
         <v>46303</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39501,7 +39510,7 @@
         <v>45804</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39579,7 +39588,7 @@
         <v>46238</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39652,7 +39661,7 @@
         <v>46238</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39725,7 +39734,7 @@
         <v>46266</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39798,7 +39807,7 @@
         <v>46266</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39871,7 +39880,7 @@
         <v>46238</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39944,7 +39953,7 @@
         <v>46238</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40017,7 +40026,7 @@
         <v>46238</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40090,7 +40099,7 @@
         <v>45110</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40168,7 +40177,7 @@
         <v>45713</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40241,7 +40250,7 @@
         <v>45833</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40319,7 +40328,7 @@
         <v>45833</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40397,7 +40406,7 @@
         <v>45837</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40470,7 +40479,7 @@
         <v>45727</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40543,7 +40552,7 @@
         <v>45736</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40616,7 +40625,7 @@
         <v>45646</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40694,7 +40703,7 @@
         <v>45665</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40767,7 +40776,7 @@
         <v>45848</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40840,7 +40849,7 @@
         <v>44929</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40913,7 +40922,7 @@
         <v>45170</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40986,7 +40995,7 @@
         <v>44223</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41059,7 +41068,7 @@
         <v>44865</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41132,7 +41141,7 @@
         <v>45747</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41210,7 +41219,7 @@
         <v>45888</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41283,7 +41292,7 @@
         <v>45888</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41356,7 +41365,7 @@
         <v>46008</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41429,7 +41438,7 @@
         <v>46132</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41502,7 +41511,7 @@
         <v>46177</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41575,7 +41584,7 @@
         <v>46286</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>

--- a/Översikt ÅTVIDABERG.xlsx
+++ b/Översikt ÅTVIDABERG.xlsx
@@ -601,7 +601,7 @@
         <v>45853</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>46276</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>45785</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46203</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45848</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45713</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>45343</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>46154</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>45155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>45335</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46276</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>46029</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>46181</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>46206</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>44778</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>46203</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>46297</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>46029</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>46029</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>46276</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44778</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>45678</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>46084</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>45783</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>46086</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>45848</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44426</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>45783</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>46154</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>46084</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>45299</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>44949</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>44795</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>45896</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>44546</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>44841</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>45156</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>46279</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>44952</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>45156</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>44823</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>45896</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>46084</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>44778</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>44516</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>44789</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>46279</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>44964</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>45259</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>44789</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>45896</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>45938</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>45131</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>46219</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>46279</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>46112</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>44631</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>45666</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45758</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>44777</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>45111</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44874</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>45274</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>44789</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>44851</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>44621</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>44609</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>45323</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>45323</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>44862</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>45938</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>45042</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>45979</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>45323</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>45222</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>46286</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>46048</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45662</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>46084</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>46301</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>46112</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>45982</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>45565</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>45379</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>44994</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v>46154</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>44942</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>45727</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>45072</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>45072</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>44935</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>45204</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>45468</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>44582</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>44641</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>44539</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>44826</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         <v>44546</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>44827</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44573</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>44495</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>44782</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>44831</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>44586</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>44729</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>44543</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>44552</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
         <v>44531</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>44573</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>44593</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>44539</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>44838</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>44789</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>44627</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>44706</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>44789</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>44830</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>44767</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>44735</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>44683</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>44724</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>44784</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>44732</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>44860</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>44514</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>44545</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>44729</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>44760</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>45036</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>44778</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>44778</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>44622</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>45092</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>45343</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>44778</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>45362</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>45824</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>45182</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>45740</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45328</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>45334</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         <v>45896</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44618</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>45896</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>45208</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15163,7 +15163,7 @@
         <v>44917</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>44964</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>44777</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>45378</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
         <v>44972</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>45112</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>44847</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>44812</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>45916</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>45917</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>46167</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>45440</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>44881</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>45923</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>44965</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>45259</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>45259</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16414,7 +16414,7 @@
         <v>44546</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>44516</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>45932</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>46171</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
         <v>44949</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>44902</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44494</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>45316</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>45939</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>45077</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>45184</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>45222</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>45747</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>45296</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>45379</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45946</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45301</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>45946</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>44833</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>46178</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>45400</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>45415</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>44767</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44902</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>45457</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18274,7 +18274,7 @@
         <v>45548</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>46178</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>45951</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>46178</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>45763</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>45440</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>45243</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>45954</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>46185</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>46189</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>45348</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>45187</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>46195</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>45308</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>45022</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>45308</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>45072</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>45720</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>44991</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>44833</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>44831</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>46203</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>44938</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>46203</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45183</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>45982</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>45097</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>44973</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>46204</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>45982</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>45098</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>45098</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>45176</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45205</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>44942</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>45104</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45224</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>45258</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>45433</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>46044</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45217</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>45707</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45784</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>45440</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>46279</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>45261</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         <v>46279</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21750,7 +21750,7 @@
         <v>46279</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>46279</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>46279</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>46280</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22057,7 +22057,7 @@
         <v>46281</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>46239</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22203,7 +22203,7 @@
         <v>46281</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
         <v>46238</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>46239</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>46239</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
         <v>46239</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>46281</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22641,7 +22641,7 @@
         <v>46029</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>46286</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>46244</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>46244</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>46034</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>46286</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         <v>46035</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>46244</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         <v>45308</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>46286</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>46286</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>46244</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>46286</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>45796</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45671</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>46043</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>46043</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>46043</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>46043</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>46043</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24116,7 +24116,7 @@
         <v>46043</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>46045</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         <v>46287</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>46048</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>46045</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
         <v>46045</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24569,7 +24569,7 @@
         <v>45169</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         <v>46289</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>46050</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>45799</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>46050</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>46049</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         <v>46195</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25080,7 +25080,7 @@
         <v>46288</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25153,7 +25153,7 @@
         <v>46288</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>46288</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>46288</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>46288</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>45804</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>46055</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>46055</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>46055</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>46045</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>46288</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>46289</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
         <v>46034</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>46288</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>46288</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>46288</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>45267</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26361,7 +26361,7 @@
         <v>46252</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>45110</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>46035</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>45713</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>46290</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>46070</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26809,7 +26809,7 @@
         <v>46294</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>46294</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>46295</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27033,7 +27033,7 @@
         <v>46083</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>46295</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>46295</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27262,7 +27262,7 @@
         <v>46085</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>45833</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27413,7 +27413,7 @@
         <v>45833</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27491,7 +27491,7 @@
         <v>45534</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>46086</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>45837</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>46097</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27788,7 +27788,7 @@
         <v>46093</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>46099</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>45727</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28007,7 +28007,7 @@
         <v>45646</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>46203</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>46286</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>45736</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>46301</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>46301</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>46301</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>46301</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>46301</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28689,7 +28689,7 @@
         <v>45665</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28762,7 +28762,7 @@
         <v>45848</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>46301</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>45833</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>44929</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>45916</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29142,7 +29142,7 @@
         <v>45308</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>46303</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29288,7 +29288,7 @@
         <v>45170</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29361,7 +29361,7 @@
         <v>46189</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>46091</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>45833</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>45951</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
         <v>44564</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29731,7 +29731,7 @@
         <v>44872</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29809,7 +29809,7 @@
         <v>45538</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         <v>45475</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>45665</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>46303</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>45758</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>45727</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30247,7 +30247,7 @@
         <v>45572</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30320,7 +30320,7 @@
         <v>44930</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30393,7 +30393,7 @@
         <v>45784</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30466,7 +30466,7 @@
         <v>46266</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>45827</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30612,7 +30612,7 @@
         <v>46266</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30685,7 +30685,7 @@
         <v>45155</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>45525</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>46238</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>46238</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>46238</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>46238</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31123,7 +31123,7 @@
         <v>46238</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>46303</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>45666</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>45554</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31420,7 +31420,7 @@
         <v>45924</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31493,7 +31493,7 @@
         <v>44876</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31566,7 +31566,7 @@
         <v>45796</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>45736</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31712,7 +31712,7 @@
         <v>44516</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>45379</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>45379</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>44937</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>45601</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>44596</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>44631</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>44980</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>44995</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>45835</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>44888</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>45597</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32598,7 +32598,7 @@
         <v>45384</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>44931</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32744,7 +32744,7 @@
         <v>44574</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>44656</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32890,7 +32890,7 @@
         <v>44741</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>44895</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>44742</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>45415</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33182,7 +33182,7 @@
         <v>45415</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>46154</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>46154</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>45817</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33474,7 +33474,7 @@
         <v>46156</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33547,7 +33547,7 @@
         <v>45839</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>44935</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>45107</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>44970</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>44988</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33917,7 +33917,7 @@
         <v>45225</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33990,7 +33990,7 @@
         <v>44721</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>45118</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>45608</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>45608</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34292,7 +34292,7 @@
         <v>45664</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>44770</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>45182</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34511,7 +34511,7 @@
         <v>44745</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>45063</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>45114</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>44546</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34813,7 +34813,7 @@
         <v>44565</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44839</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>45229</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         <v>45090</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>44607</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>45243</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>45022</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>45334</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35397,7 +35397,7 @@
         <v>45077</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>44922</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>45250</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>44545</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>45180</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35767,7 +35767,7 @@
         <v>45180</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>45089</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>45471</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>45229</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>45740</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36132,7 +36132,7 @@
         <v>45104</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36210,7 +36210,7 @@
         <v>45104</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45387</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45122</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>44915</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>45358</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>44495</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>44742</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>45167</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36799,7 +36799,7 @@
         <v>45384</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>45040</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36945,7 +36945,7 @@
         <v>45168</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>45122</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37096,7 +37096,7 @@
         <v>45040</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37169,7 +37169,7 @@
         <v>45315</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>45415</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>45334</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>44579</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37461,7 +37461,7 @@
         <v>45169</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45187</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
         <v>45483</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>44988</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>45555</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45442</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>44806</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37972,7 +37972,7 @@
         <v>45685</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38045,7 +38045,7 @@
         <v>44586</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>44621</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38191,7 +38191,7 @@
         <v>45153</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38264,7 +38264,7 @@
         <v>45224</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>44777</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         <v>45113</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38493,7 +38493,7 @@
         <v>45707</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>45168</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>45715</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38717,7 +38717,7 @@
         <v>45665</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38790,7 +38790,7 @@
         <v>44817</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38863,7 +38863,7 @@
         <v>44721</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38936,7 +38936,7 @@
         <v>44721</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39009,7 +39009,7 @@
         <v>44735</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>45225</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39155,7 +39155,7 @@
         <v>44806</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>45695</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39301,7 +39301,7 @@
         <v>45229</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>45229</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45296</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>44767</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>45217</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>45097</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39739,7 +39739,7 @@
         <v>44938</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>45323</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>44851</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>45296</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>44784</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>44629</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40177,7 +40177,7 @@
         <v>45362</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>44791</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>44517</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40401,7 +40401,7 @@
         <v>44938</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>44897</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>44582</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>44745</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>44967</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>44223</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40839,7 +40839,7 @@
         <v>44865</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>45747</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40990,7 +40990,7 @@
         <v>45888</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41063,7 +41063,7 @@
         <v>45888</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>46008</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41209,7 +41209,7 @@
         <v>46132</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>46177</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>46286</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>

--- a/Översikt ÅTVIDABERG.xlsx
+++ b/Översikt ÅTVIDABERG.xlsx
@@ -601,7 +601,7 @@
         <v>45853</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>46276</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>45785</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>46203</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45848</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45713</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>45343</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>46154</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>45155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>45335</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46276</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>46029</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>46181</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>46206</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>44778</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>46203</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>46297</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>46029</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>46029</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>46276</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44778</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>45678</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>46084</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>45783</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>46086</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>45848</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44426</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>45783</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>46154</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>46084</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>45299</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>44949</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>44795</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>45896</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>44546</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>44841</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>45156</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>46279</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>44952</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>45156</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>44823</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>45896</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>46084</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>44778</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>44516</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>44789</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>46279</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>44964</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>45259</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>44789</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>45896</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>45938</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>45131</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>46219</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>46279</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>46112</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>44631</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>45666</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45758</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>44777</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>45111</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44874</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>45274</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>44789</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>44851</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>44621</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>44609</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>45323</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>45323</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>44862</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>45938</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>45042</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>45979</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>45323</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>45222</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>46286</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>46048</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45662</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>46084</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>46301</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>46112</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>45982</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>45565</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>45379</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>44994</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v>46154</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>44942</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>45727</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>45072</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>45072</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>44935</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>45204</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>45468</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>44582</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>44641</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>44539</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>44826</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         <v>44546</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>44827</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44573</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>44495</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>44782</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>44831</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>44586</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>44729</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>44543</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>44552</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
         <v>44531</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>44573</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>44593</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>44539</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>44838</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>44789</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>44627</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>44706</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>44789</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>44830</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>44767</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>44735</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>44683</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>44724</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>44784</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>44732</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>44860</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>44514</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>44545</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>44729</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>44760</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>45036</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>44778</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>44778</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>44622</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>45092</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>45343</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>44778</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>45362</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>45824</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>45182</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>45740</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45328</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>45334</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         <v>45896</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44618</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>45896</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>45208</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15163,7 +15163,7 @@
         <v>44917</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>44964</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>44777</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>45378</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
         <v>44972</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>45112</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>44847</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>44812</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>45916</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>45917</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>46167</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>45440</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>44881</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>45923</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>44965</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>45259</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>45259</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16414,7 +16414,7 @@
         <v>44546</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>44516</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>45932</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>46171</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
         <v>44949</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>44902</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44494</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>45316</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>45939</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>45077</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>45184</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>45222</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>45747</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>45296</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>45379</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45946</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45301</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>45946</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>44833</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>46178</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>45400</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>45415</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>44767</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44902</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>45457</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18274,7 +18274,7 @@
         <v>45548</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>46178</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>45951</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>46178</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>45763</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>45440</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>45243</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>45954</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>46185</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>46189</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>45348</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>45187</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>46195</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>45308</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>45022</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>45308</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>45072</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>45720</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>44991</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>44833</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>44831</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>46203</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>44938</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>46203</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45183</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>45982</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>45097</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>44973</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>46204</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>45982</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>45098</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>45098</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>45176</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45205</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>44942</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>45104</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45224</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>45258</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>45433</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>46044</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45217</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>45707</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45784</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>45440</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>46279</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>45261</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         <v>46279</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21750,7 +21750,7 @@
         <v>46279</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>46279</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>46279</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>46280</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22057,7 +22057,7 @@
         <v>46281</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>46239</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22203,7 +22203,7 @@
         <v>46281</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
         <v>46238</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>46239</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>46239</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
         <v>46239</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>46281</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22641,7 +22641,7 @@
         <v>46029</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>46286</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>46244</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>46244</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>46034</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>46286</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         <v>46035</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>46244</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         <v>45308</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>46286</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>46286</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>46244</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>46286</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>45796</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45671</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>46043</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>46043</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>46043</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>46043</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>46043</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24116,7 +24116,7 @@
         <v>46043</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>46045</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         <v>46287</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>46048</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>46045</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
         <v>46045</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24569,7 +24569,7 @@
         <v>45169</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         <v>46289</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>46050</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>45799</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>46050</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>46049</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         <v>46195</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25080,7 +25080,7 @@
         <v>46288</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25153,7 +25153,7 @@
         <v>46288</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>46288</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>46288</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>46288</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>45804</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>46055</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>46055</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>46055</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>46045</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>46288</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>46289</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
         <v>46034</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>46288</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>46288</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>46288</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>45267</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26361,7 +26361,7 @@
         <v>46252</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>45110</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>46035</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>45713</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>46290</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>46070</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26809,7 +26809,7 @@
         <v>46294</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>46294</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>46295</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27033,7 +27033,7 @@
         <v>46083</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>46295</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>46295</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27262,7 +27262,7 @@
         <v>46085</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>45833</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27413,7 +27413,7 @@
         <v>45833</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27491,7 +27491,7 @@
         <v>45534</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>46086</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>45837</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>46097</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27788,7 +27788,7 @@
         <v>46093</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>46099</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>45727</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28007,7 +28007,7 @@
         <v>45646</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>46203</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>46286</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>45736</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>46301</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>46301</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>46301</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>46301</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>46301</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28689,7 +28689,7 @@
         <v>45665</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28762,7 +28762,7 @@
         <v>45848</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>46301</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>45833</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>44929</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>45916</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29142,7 +29142,7 @@
         <v>45308</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>46303</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29288,7 +29288,7 @@
         <v>45170</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29361,7 +29361,7 @@
         <v>46189</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>46091</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>45833</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>45951</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
         <v>44564</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29731,7 +29731,7 @@
         <v>44872</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29809,7 +29809,7 @@
         <v>45538</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         <v>45475</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>45665</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>46303</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>45758</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>45727</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30247,7 +30247,7 @@
         <v>45572</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30320,7 +30320,7 @@
         <v>44930</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30393,7 +30393,7 @@
         <v>45784</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30466,7 +30466,7 @@
         <v>46266</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>45827</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30612,7 +30612,7 @@
         <v>46266</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30685,7 +30685,7 @@
         <v>45155</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>45525</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>46238</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>46238</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>46238</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>46238</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31123,7 +31123,7 @@
         <v>46238</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>46303</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>45666</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>45554</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31420,7 +31420,7 @@
         <v>45924</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31493,7 +31493,7 @@
         <v>44876</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31566,7 +31566,7 @@
         <v>45796</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>45736</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31712,7 +31712,7 @@
         <v>44516</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>45379</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>45379</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>44937</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>45601</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>44596</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>44631</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>44980</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>44995</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>45835</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>44888</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>45597</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32598,7 +32598,7 @@
         <v>45384</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>44931</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32744,7 +32744,7 @@
         <v>44574</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>44656</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32890,7 +32890,7 @@
         <v>44741</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>44895</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>44742</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>45415</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33182,7 +33182,7 @@
         <v>45415</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>46154</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>46154</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>45817</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33474,7 +33474,7 @@
         <v>46156</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33547,7 +33547,7 @@
         <v>45839</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>44935</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>45107</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>44970</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>44988</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33917,7 +33917,7 @@
         <v>45225</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33990,7 +33990,7 @@
         <v>44721</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>45118</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>45608</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>45608</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34292,7 +34292,7 @@
         <v>45664</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>44770</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>45182</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34511,7 +34511,7 @@
         <v>44745</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>45063</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>45114</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>44546</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34813,7 +34813,7 @@
         <v>44565</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44839</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>45229</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         <v>45090</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>44607</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>45243</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>45022</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>45334</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35397,7 +35397,7 @@
         <v>45077</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>44922</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>45250</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>44545</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>45180</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35767,7 +35767,7 @@
         <v>45180</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>45089</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>45471</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>45229</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>45740</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36132,7 +36132,7 @@
         <v>45104</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36210,7 +36210,7 @@
         <v>45104</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45387</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45122</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>44915</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>45358</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>44495</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>44742</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>45167</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36799,7 +36799,7 @@
         <v>45384</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>45040</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36945,7 +36945,7 @@
         <v>45168</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>45122</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37096,7 +37096,7 @@
         <v>45040</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37169,7 +37169,7 @@
         <v>45315</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>45415</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>45334</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>44579</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37461,7 +37461,7 @@
         <v>45169</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45187</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
         <v>45483</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>44988</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>45555</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45442</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>44806</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37972,7 +37972,7 @@
         <v>45685</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38045,7 +38045,7 @@
         <v>44586</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>44621</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38191,7 +38191,7 @@
         <v>45153</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38264,7 +38264,7 @@
         <v>45224</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>44777</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         <v>45113</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38493,7 +38493,7 @@
         <v>45707</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>45168</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>45715</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38717,7 +38717,7 @@
         <v>45665</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38790,7 +38790,7 @@
         <v>44817</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38863,7 +38863,7 @@
         <v>44721</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38936,7 +38936,7 @@
         <v>44721</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39009,7 +39009,7 @@
         <v>44735</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>45225</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39155,7 +39155,7 @@
         <v>44806</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>45695</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39301,7 +39301,7 @@
         <v>45229</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>45229</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45296</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>44767</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>45217</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>45097</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39739,7 +39739,7 @@
         <v>44938</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>45323</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>44851</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>45296</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>44784</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>44629</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40177,7 +40177,7 @@
         <v>45362</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>44791</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>44517</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40401,7 +40401,7 @@
         <v>44938</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>44897</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>44582</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>44745</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>44967</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>44223</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40839,7 +40839,7 @@
         <v>44865</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>45747</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40990,7 +40990,7 @@
         <v>45888</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41063,7 +41063,7 @@
         <v>45888</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>46008</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41209,7 +41209,7 @@
         <v>46132</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>46177</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>46286</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
